--- a/data/processed/recettes_secteur.xlsx
+++ b/data/processed/recettes_secteur.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G128"/>
+  <dimension ref="A1:T128"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -471,6 +471,71 @@
           <t>date</t>
         </is>
       </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>trimestre</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>month_sin</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>month_cos</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>lag_1</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>lag_3</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>lag_6</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>moyenne_mobile</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>rolling_6</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>transactions_lag_1</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>transactions_lag_3</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>transactions_rolling_3</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>transactions_diff</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>trend</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -485,7 +550,7 @@
         <v>1</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>44927</v>
+        <v>44957</v>
       </c>
       <c r="E2" t="n">
         <v>37700</v>
@@ -494,7 +559,28 @@
         <v>474</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>44927</v>
+        <v>44957</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0.4999999999999999</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0.8660254037844387</v>
+      </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr"/>
+      <c r="T2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -510,7 +596,7 @@
         <v>2</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>44958</v>
+        <v>44985</v>
       </c>
       <c r="E3" t="n">
         <v>38449</v>
@@ -519,7 +605,34 @@
         <v>426</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>44958</v>
+        <v>44985</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.8660254037844386</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0.5000000000000001</v>
+      </c>
+      <c r="K3" t="n">
+        <v>37700</v>
+      </c>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="n">
+        <v>474</v>
+      </c>
+      <c r="Q3" t="inlineStr"/>
+      <c r="R3" t="inlineStr"/>
+      <c r="S3" t="n">
+        <v>-48</v>
+      </c>
+      <c r="T3" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -535,7 +648,7 @@
         <v>3</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>44986</v>
+        <v>45016</v>
       </c>
       <c r="E4" t="n">
         <v>34150</v>
@@ -544,7 +657,34 @@
         <v>364</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>44986</v>
+        <v>45016</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J4" t="n">
+        <v>6.123233995736766e-17</v>
+      </c>
+      <c r="K4" t="n">
+        <v>38449</v>
+      </c>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="n">
+        <v>426</v>
+      </c>
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr"/>
+      <c r="S4" t="n">
+        <v>-62</v>
+      </c>
+      <c r="T4" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="5">
@@ -560,7 +700,7 @@
         <v>4</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>45017</v>
+        <v>45046</v>
       </c>
       <c r="E5" t="n">
         <v>28516</v>
@@ -569,7 +709,42 @@
         <v>331</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>45017</v>
+        <v>45046</v>
+      </c>
+      <c r="H5" t="n">
+        <v>2</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.8660254037844387</v>
+      </c>
+      <c r="J5" t="n">
+        <v>-0.4999999999999998</v>
+      </c>
+      <c r="K5" t="n">
+        <v>34150</v>
+      </c>
+      <c r="L5" t="n">
+        <v>37700</v>
+      </c>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="n">
+        <v>36766.33333333334</v>
+      </c>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="n">
+        <v>364</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>474</v>
+      </c>
+      <c r="R5" t="n">
+        <v>421.3333333333333</v>
+      </c>
+      <c r="S5" t="n">
+        <v>-33</v>
+      </c>
+      <c r="T5" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="6">
@@ -585,7 +760,7 @@
         <v>5</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>45047</v>
+        <v>45077</v>
       </c>
       <c r="E6" t="n">
         <v>36949</v>
@@ -594,7 +769,42 @@
         <v>420</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>45047</v>
+        <v>45077</v>
+      </c>
+      <c r="H6" t="n">
+        <v>2</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.4999999999999999</v>
+      </c>
+      <c r="J6" t="n">
+        <v>-0.8660254037844387</v>
+      </c>
+      <c r="K6" t="n">
+        <v>28516</v>
+      </c>
+      <c r="L6" t="n">
+        <v>38449</v>
+      </c>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="n">
+        <v>33705</v>
+      </c>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="n">
+        <v>331</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>426</v>
+      </c>
+      <c r="R6" t="n">
+        <v>373.6666666666667</v>
+      </c>
+      <c r="S6" t="n">
+        <v>89</v>
+      </c>
+      <c r="T6" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="7">
@@ -610,7 +820,7 @@
         <v>6</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>45078</v>
+        <v>45107</v>
       </c>
       <c r="E7" t="n">
         <v>33913</v>
@@ -619,7 +829,42 @@
         <v>315</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>45078</v>
+        <v>45107</v>
+      </c>
+      <c r="H7" t="n">
+        <v>2</v>
+      </c>
+      <c r="I7" t="n">
+        <v>1.224646799147353e-16</v>
+      </c>
+      <c r="J7" t="n">
+        <v>-1</v>
+      </c>
+      <c r="K7" t="n">
+        <v>36949</v>
+      </c>
+      <c r="L7" t="n">
+        <v>34150</v>
+      </c>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="n">
+        <v>33205</v>
+      </c>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="n">
+        <v>420</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>364</v>
+      </c>
+      <c r="R7" t="n">
+        <v>371.6666666666667</v>
+      </c>
+      <c r="S7" t="n">
+        <v>-105</v>
+      </c>
+      <c r="T7" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="8">
@@ -635,7 +880,7 @@
         <v>7</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>45108</v>
+        <v>45138</v>
       </c>
       <c r="E8" t="n">
         <v>16939</v>
@@ -644,7 +889,46 @@
         <v>173</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>45108</v>
+        <v>45138</v>
+      </c>
+      <c r="H8" t="n">
+        <v>3</v>
+      </c>
+      <c r="I8" t="n">
+        <v>-0.4999999999999997</v>
+      </c>
+      <c r="J8" t="n">
+        <v>-0.8660254037844388</v>
+      </c>
+      <c r="K8" t="n">
+        <v>33913</v>
+      </c>
+      <c r="L8" t="n">
+        <v>28516</v>
+      </c>
+      <c r="M8" t="n">
+        <v>37700</v>
+      </c>
+      <c r="N8" t="n">
+        <v>33126</v>
+      </c>
+      <c r="O8" t="n">
+        <v>34946.16666666666</v>
+      </c>
+      <c r="P8" t="n">
+        <v>315</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>331</v>
+      </c>
+      <c r="R8" t="n">
+        <v>355.3333333333333</v>
+      </c>
+      <c r="S8" t="n">
+        <v>-142</v>
+      </c>
+      <c r="T8" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="9">
@@ -660,7 +944,7 @@
         <v>8</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>45139</v>
+        <v>45169</v>
       </c>
       <c r="E9" t="n">
         <v>31286</v>
@@ -669,7 +953,46 @@
         <v>297</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>45139</v>
+        <v>45169</v>
+      </c>
+      <c r="H9" t="n">
+        <v>3</v>
+      </c>
+      <c r="I9" t="n">
+        <v>-0.8660254037844385</v>
+      </c>
+      <c r="J9" t="n">
+        <v>-0.5000000000000004</v>
+      </c>
+      <c r="K9" t="n">
+        <v>16939</v>
+      </c>
+      <c r="L9" t="n">
+        <v>36949</v>
+      </c>
+      <c r="M9" t="n">
+        <v>38449</v>
+      </c>
+      <c r="N9" t="n">
+        <v>29267</v>
+      </c>
+      <c r="O9" t="n">
+        <v>31486</v>
+      </c>
+      <c r="P9" t="n">
+        <v>173</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>420</v>
+      </c>
+      <c r="R9" t="n">
+        <v>302.6666666666667</v>
+      </c>
+      <c r="S9" t="n">
+        <v>124</v>
+      </c>
+      <c r="T9" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="10">
@@ -685,7 +1008,7 @@
         <v>9</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>45170</v>
+        <v>45199</v>
       </c>
       <c r="E10" t="n">
         <v>39041</v>
@@ -694,7 +1017,46 @@
         <v>379</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>45170</v>
+        <v>45199</v>
+      </c>
+      <c r="H10" t="n">
+        <v>3</v>
+      </c>
+      <c r="I10" t="n">
+        <v>-1</v>
+      </c>
+      <c r="J10" t="n">
+        <v>-1.83697019872103e-16</v>
+      </c>
+      <c r="K10" t="n">
+        <v>31286</v>
+      </c>
+      <c r="L10" t="n">
+        <v>33913</v>
+      </c>
+      <c r="M10" t="n">
+        <v>34150</v>
+      </c>
+      <c r="N10" t="n">
+        <v>27379.33333333333</v>
+      </c>
+      <c r="O10" t="n">
+        <v>30292.16666666667</v>
+      </c>
+      <c r="P10" t="n">
+        <v>297</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>315</v>
+      </c>
+      <c r="R10" t="n">
+        <v>261.6666666666667</v>
+      </c>
+      <c r="S10" t="n">
+        <v>82</v>
+      </c>
+      <c r="T10" t="n">
+        <v>8</v>
       </c>
     </row>
     <row r="11">
@@ -710,7 +1072,7 @@
         <v>10</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>45200</v>
+        <v>45230</v>
       </c>
       <c r="E11" t="n">
         <v>36751</v>
@@ -719,7 +1081,46 @@
         <v>440</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>45200</v>
+        <v>45230</v>
+      </c>
+      <c r="H11" t="n">
+        <v>4</v>
+      </c>
+      <c r="I11" t="n">
+        <v>-0.8660254037844386</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0.5000000000000001</v>
+      </c>
+      <c r="K11" t="n">
+        <v>39041</v>
+      </c>
+      <c r="L11" t="n">
+        <v>16939</v>
+      </c>
+      <c r="M11" t="n">
+        <v>28516</v>
+      </c>
+      <c r="N11" t="n">
+        <v>29088.66666666667</v>
+      </c>
+      <c r="O11" t="n">
+        <v>31107.33333333333</v>
+      </c>
+      <c r="P11" t="n">
+        <v>379</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>173</v>
+      </c>
+      <c r="R11" t="n">
+        <v>283</v>
+      </c>
+      <c r="S11" t="n">
+        <v>61</v>
+      </c>
+      <c r="T11" t="n">
+        <v>9</v>
       </c>
     </row>
     <row r="12">
@@ -735,7 +1136,7 @@
         <v>11</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>45231</v>
+        <v>45260</v>
       </c>
       <c r="E12" t="n">
         <v>46001</v>
@@ -744,7 +1145,46 @@
         <v>467</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>45231</v>
+        <v>45260</v>
+      </c>
+      <c r="H12" t="n">
+        <v>4</v>
+      </c>
+      <c r="I12" t="n">
+        <v>-0.5000000000000004</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0.8660254037844384</v>
+      </c>
+      <c r="K12" t="n">
+        <v>36751</v>
+      </c>
+      <c r="L12" t="n">
+        <v>31286</v>
+      </c>
+      <c r="M12" t="n">
+        <v>36949</v>
+      </c>
+      <c r="N12" t="n">
+        <v>35692.66666666666</v>
+      </c>
+      <c r="O12" t="n">
+        <v>32479.83333333333</v>
+      </c>
+      <c r="P12" t="n">
+        <v>440</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>297</v>
+      </c>
+      <c r="R12" t="n">
+        <v>372</v>
+      </c>
+      <c r="S12" t="n">
+        <v>27</v>
+      </c>
+      <c r="T12" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="13">
@@ -760,7 +1200,7 @@
         <v>12</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>45261</v>
+        <v>45291</v>
       </c>
       <c r="E13" t="n">
         <v>41212</v>
@@ -769,7 +1209,46 @@
         <v>394</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>45261</v>
+        <v>45291</v>
+      </c>
+      <c r="H13" t="n">
+        <v>4</v>
+      </c>
+      <c r="I13" t="n">
+        <v>-2.449293598294706e-16</v>
+      </c>
+      <c r="J13" t="n">
+        <v>1</v>
+      </c>
+      <c r="K13" t="n">
+        <v>46001</v>
+      </c>
+      <c r="L13" t="n">
+        <v>39041</v>
+      </c>
+      <c r="M13" t="n">
+        <v>33913</v>
+      </c>
+      <c r="N13" t="n">
+        <v>40597.66666666666</v>
+      </c>
+      <c r="O13" t="n">
+        <v>33988.5</v>
+      </c>
+      <c r="P13" t="n">
+        <v>467</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>379</v>
+      </c>
+      <c r="R13" t="n">
+        <v>428.6666666666667</v>
+      </c>
+      <c r="S13" t="n">
+        <v>-73</v>
+      </c>
+      <c r="T13" t="n">
+        <v>11</v>
       </c>
     </row>
     <row r="14">
@@ -785,7 +1264,7 @@
         <v>1</v>
       </c>
       <c r="D14" s="2" t="n">
-        <v>45292</v>
+        <v>45322</v>
       </c>
       <c r="E14" t="n">
         <v>45085</v>
@@ -794,7 +1273,46 @@
         <v>471</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>45292</v>
+        <v>45322</v>
+      </c>
+      <c r="H14" t="n">
+        <v>1</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0.4999999999999999</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0.8660254037844387</v>
+      </c>
+      <c r="K14" t="n">
+        <v>41212</v>
+      </c>
+      <c r="L14" t="n">
+        <v>36751</v>
+      </c>
+      <c r="M14" t="n">
+        <v>16939</v>
+      </c>
+      <c r="N14" t="n">
+        <v>41321.33333333334</v>
+      </c>
+      <c r="O14" t="n">
+        <v>35205</v>
+      </c>
+      <c r="P14" t="n">
+        <v>394</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>440</v>
+      </c>
+      <c r="R14" t="n">
+        <v>433.6666666666667</v>
+      </c>
+      <c r="S14" t="n">
+        <v>77</v>
+      </c>
+      <c r="T14" t="n">
+        <v>12</v>
       </c>
     </row>
     <row r="15">
@@ -810,7 +1328,7 @@
         <v>2</v>
       </c>
       <c r="D15" s="2" t="n">
-        <v>45323</v>
+        <v>45351</v>
       </c>
       <c r="E15" t="n">
         <v>44313</v>
@@ -819,7 +1337,46 @@
         <v>463</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>45323</v>
+        <v>45351</v>
+      </c>
+      <c r="H15" t="n">
+        <v>1</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0.8660254037844386</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0.5000000000000001</v>
+      </c>
+      <c r="K15" t="n">
+        <v>45085</v>
+      </c>
+      <c r="L15" t="n">
+        <v>46001</v>
+      </c>
+      <c r="M15" t="n">
+        <v>31286</v>
+      </c>
+      <c r="N15" t="n">
+        <v>44099.33333333334</v>
+      </c>
+      <c r="O15" t="n">
+        <v>39896</v>
+      </c>
+      <c r="P15" t="n">
+        <v>471</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>467</v>
+      </c>
+      <c r="R15" t="n">
+        <v>444</v>
+      </c>
+      <c r="S15" t="n">
+        <v>-8</v>
+      </c>
+      <c r="T15" t="n">
+        <v>13</v>
       </c>
     </row>
     <row r="16">
@@ -835,7 +1392,7 @@
         <v>3</v>
       </c>
       <c r="D16" s="2" t="n">
-        <v>45352</v>
+        <v>45382</v>
       </c>
       <c r="E16" t="n">
         <v>25100</v>
@@ -844,7 +1401,46 @@
         <v>307</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>45352</v>
+        <v>45382</v>
+      </c>
+      <c r="H16" t="n">
+        <v>1</v>
+      </c>
+      <c r="I16" t="n">
+        <v>1</v>
+      </c>
+      <c r="J16" t="n">
+        <v>6.123233995736766e-17</v>
+      </c>
+      <c r="K16" t="n">
+        <v>44313</v>
+      </c>
+      <c r="L16" t="n">
+        <v>41212</v>
+      </c>
+      <c r="M16" t="n">
+        <v>39041</v>
+      </c>
+      <c r="N16" t="n">
+        <v>43536.66666666666</v>
+      </c>
+      <c r="O16" t="n">
+        <v>42067.16666666666</v>
+      </c>
+      <c r="P16" t="n">
+        <v>463</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>394</v>
+      </c>
+      <c r="R16" t="n">
+        <v>442.6666666666667</v>
+      </c>
+      <c r="S16" t="n">
+        <v>-156</v>
+      </c>
+      <c r="T16" t="n">
+        <v>14</v>
       </c>
     </row>
     <row r="17">
@@ -860,7 +1456,7 @@
         <v>4</v>
       </c>
       <c r="D17" s="2" t="n">
-        <v>45383</v>
+        <v>45412</v>
       </c>
       <c r="E17" t="n">
         <v>45969</v>
@@ -869,7 +1465,46 @@
         <v>383</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>45383</v>
+        <v>45412</v>
+      </c>
+      <c r="H17" t="n">
+        <v>2</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0.8660254037844387</v>
+      </c>
+      <c r="J17" t="n">
+        <v>-0.4999999999999998</v>
+      </c>
+      <c r="K17" t="n">
+        <v>25100</v>
+      </c>
+      <c r="L17" t="n">
+        <v>45085</v>
+      </c>
+      <c r="M17" t="n">
+        <v>36751</v>
+      </c>
+      <c r="N17" t="n">
+        <v>38166</v>
+      </c>
+      <c r="O17" t="n">
+        <v>39743.66666666666</v>
+      </c>
+      <c r="P17" t="n">
+        <v>307</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>471</v>
+      </c>
+      <c r="R17" t="n">
+        <v>413.6666666666667</v>
+      </c>
+      <c r="S17" t="n">
+        <v>76</v>
+      </c>
+      <c r="T17" t="n">
+        <v>15</v>
       </c>
     </row>
     <row r="18">
@@ -885,7 +1520,7 @@
         <v>5</v>
       </c>
       <c r="D18" s="2" t="n">
-        <v>45413</v>
+        <v>45443</v>
       </c>
       <c r="E18" t="n">
         <v>40799</v>
@@ -894,7 +1529,46 @@
         <v>374</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>45413</v>
+        <v>45443</v>
+      </c>
+      <c r="H18" t="n">
+        <v>2</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0.4999999999999999</v>
+      </c>
+      <c r="J18" t="n">
+        <v>-0.8660254037844387</v>
+      </c>
+      <c r="K18" t="n">
+        <v>45969</v>
+      </c>
+      <c r="L18" t="n">
+        <v>44313</v>
+      </c>
+      <c r="M18" t="n">
+        <v>46001</v>
+      </c>
+      <c r="N18" t="n">
+        <v>38460.66666666666</v>
+      </c>
+      <c r="O18" t="n">
+        <v>41280</v>
+      </c>
+      <c r="P18" t="n">
+        <v>383</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>463</v>
+      </c>
+      <c r="R18" t="n">
+        <v>384.3333333333333</v>
+      </c>
+      <c r="S18" t="n">
+        <v>-9</v>
+      </c>
+      <c r="T18" t="n">
+        <v>16</v>
       </c>
     </row>
     <row r="19">
@@ -910,7 +1584,7 @@
         <v>6</v>
       </c>
       <c r="D19" s="2" t="n">
-        <v>45444</v>
+        <v>45473</v>
       </c>
       <c r="E19" t="n">
         <v>218995</v>
@@ -919,7 +1593,46 @@
         <v>406</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>45444</v>
+        <v>45473</v>
+      </c>
+      <c r="H19" t="n">
+        <v>2</v>
+      </c>
+      <c r="I19" t="n">
+        <v>1.224646799147353e-16</v>
+      </c>
+      <c r="J19" t="n">
+        <v>-1</v>
+      </c>
+      <c r="K19" t="n">
+        <v>40799</v>
+      </c>
+      <c r="L19" t="n">
+        <v>25100</v>
+      </c>
+      <c r="M19" t="n">
+        <v>41212</v>
+      </c>
+      <c r="N19" t="n">
+        <v>37289.33333333334</v>
+      </c>
+      <c r="O19" t="n">
+        <v>40413</v>
+      </c>
+      <c r="P19" t="n">
+        <v>374</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>307</v>
+      </c>
+      <c r="R19" t="n">
+        <v>354.6666666666667</v>
+      </c>
+      <c r="S19" t="n">
+        <v>32</v>
+      </c>
+      <c r="T19" t="n">
+        <v>17</v>
       </c>
     </row>
     <row r="20">
@@ -935,7 +1648,7 @@
         <v>7</v>
       </c>
       <c r="D20" s="2" t="n">
-        <v>45474</v>
+        <v>45504</v>
       </c>
       <c r="E20" t="n">
         <v>45828</v>
@@ -944,7 +1657,46 @@
         <v>316</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>45474</v>
+        <v>45504</v>
+      </c>
+      <c r="H20" t="n">
+        <v>3</v>
+      </c>
+      <c r="I20" t="n">
+        <v>-0.4999999999999997</v>
+      </c>
+      <c r="J20" t="n">
+        <v>-0.8660254037844388</v>
+      </c>
+      <c r="K20" t="n">
+        <v>218995</v>
+      </c>
+      <c r="L20" t="n">
+        <v>45969</v>
+      </c>
+      <c r="M20" t="n">
+        <v>45085</v>
+      </c>
+      <c r="N20" t="n">
+        <v>101921</v>
+      </c>
+      <c r="O20" t="n">
+        <v>70043.5</v>
+      </c>
+      <c r="P20" t="n">
+        <v>406</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>383</v>
+      </c>
+      <c r="R20" t="n">
+        <v>387.6666666666667</v>
+      </c>
+      <c r="S20" t="n">
+        <v>-90</v>
+      </c>
+      <c r="T20" t="n">
+        <v>18</v>
       </c>
     </row>
     <row r="21">
@@ -960,7 +1712,7 @@
         <v>8</v>
       </c>
       <c r="D21" s="2" t="n">
-        <v>45505</v>
+        <v>45535</v>
       </c>
       <c r="E21" t="n">
         <v>32741</v>
@@ -969,7 +1721,46 @@
         <v>297</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>45505</v>
+        <v>45535</v>
+      </c>
+      <c r="H21" t="n">
+        <v>3</v>
+      </c>
+      <c r="I21" t="n">
+        <v>-0.8660254037844385</v>
+      </c>
+      <c r="J21" t="n">
+        <v>-0.5000000000000004</v>
+      </c>
+      <c r="K21" t="n">
+        <v>45828</v>
+      </c>
+      <c r="L21" t="n">
+        <v>40799</v>
+      </c>
+      <c r="M21" t="n">
+        <v>44313</v>
+      </c>
+      <c r="N21" t="n">
+        <v>101874</v>
+      </c>
+      <c r="O21" t="n">
+        <v>70167.33333333333</v>
+      </c>
+      <c r="P21" t="n">
+        <v>316</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>374</v>
+      </c>
+      <c r="R21" t="n">
+        <v>365.3333333333333</v>
+      </c>
+      <c r="S21" t="n">
+        <v>-19</v>
+      </c>
+      <c r="T21" t="n">
+        <v>19</v>
       </c>
     </row>
     <row r="22">
@@ -985,7 +1776,7 @@
         <v>9</v>
       </c>
       <c r="D22" s="2" t="n">
-        <v>45536</v>
+        <v>45565</v>
       </c>
       <c r="E22" t="n">
         <v>30882</v>
@@ -994,7 +1785,46 @@
         <v>327</v>
       </c>
       <c r="G22" s="3" t="n">
-        <v>45536</v>
+        <v>45565</v>
+      </c>
+      <c r="H22" t="n">
+        <v>3</v>
+      </c>
+      <c r="I22" t="n">
+        <v>-1</v>
+      </c>
+      <c r="J22" t="n">
+        <v>-1.83697019872103e-16</v>
+      </c>
+      <c r="K22" t="n">
+        <v>32741</v>
+      </c>
+      <c r="L22" t="n">
+        <v>218995</v>
+      </c>
+      <c r="M22" t="n">
+        <v>25100</v>
+      </c>
+      <c r="N22" t="n">
+        <v>99188</v>
+      </c>
+      <c r="O22" t="n">
+        <v>68238.66666666667</v>
+      </c>
+      <c r="P22" t="n">
+        <v>297</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>406</v>
+      </c>
+      <c r="R22" t="n">
+        <v>339.6666666666667</v>
+      </c>
+      <c r="S22" t="n">
+        <v>30</v>
+      </c>
+      <c r="T22" t="n">
+        <v>20</v>
       </c>
     </row>
     <row r="23">
@@ -1010,7 +1840,7 @@
         <v>10</v>
       </c>
       <c r="D23" s="2" t="n">
-        <v>45566</v>
+        <v>45596</v>
       </c>
       <c r="E23" t="n">
         <v>54426</v>
@@ -1019,7 +1849,46 @@
         <v>469</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>45566</v>
+        <v>45596</v>
+      </c>
+      <c r="H23" t="n">
+        <v>4</v>
+      </c>
+      <c r="I23" t="n">
+        <v>-0.8660254037844386</v>
+      </c>
+      <c r="J23" t="n">
+        <v>0.5000000000000001</v>
+      </c>
+      <c r="K23" t="n">
+        <v>30882</v>
+      </c>
+      <c r="L23" t="n">
+        <v>45828</v>
+      </c>
+      <c r="M23" t="n">
+        <v>45969</v>
+      </c>
+      <c r="N23" t="n">
+        <v>36483.66666666666</v>
+      </c>
+      <c r="O23" t="n">
+        <v>69202.33333333333</v>
+      </c>
+      <c r="P23" t="n">
+        <v>327</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>316</v>
+      </c>
+      <c r="R23" t="n">
+        <v>313.3333333333333</v>
+      </c>
+      <c r="S23" t="n">
+        <v>142</v>
+      </c>
+      <c r="T23" t="n">
+        <v>21</v>
       </c>
     </row>
     <row r="24">
@@ -1035,7 +1904,7 @@
         <v>11</v>
       </c>
       <c r="D24" s="2" t="n">
-        <v>45597</v>
+        <v>45626</v>
       </c>
       <c r="E24" t="n">
         <v>52636</v>
@@ -1044,7 +1913,46 @@
         <v>378</v>
       </c>
       <c r="G24" s="3" t="n">
-        <v>45597</v>
+        <v>45626</v>
+      </c>
+      <c r="H24" t="n">
+        <v>4</v>
+      </c>
+      <c r="I24" t="n">
+        <v>-0.5000000000000004</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0.8660254037844384</v>
+      </c>
+      <c r="K24" t="n">
+        <v>54426</v>
+      </c>
+      <c r="L24" t="n">
+        <v>32741</v>
+      </c>
+      <c r="M24" t="n">
+        <v>40799</v>
+      </c>
+      <c r="N24" t="n">
+        <v>39349.66666666666</v>
+      </c>
+      <c r="O24" t="n">
+        <v>70611.83333333333</v>
+      </c>
+      <c r="P24" t="n">
+        <v>469</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>297</v>
+      </c>
+      <c r="R24" t="n">
+        <v>364.3333333333333</v>
+      </c>
+      <c r="S24" t="n">
+        <v>-91</v>
+      </c>
+      <c r="T24" t="n">
+        <v>22</v>
       </c>
     </row>
     <row r="25">
@@ -1060,7 +1968,7 @@
         <v>12</v>
       </c>
       <c r="D25" s="2" t="n">
-        <v>45627</v>
+        <v>45657</v>
       </c>
       <c r="E25" t="n">
         <v>55407</v>
@@ -1069,7 +1977,46 @@
         <v>403</v>
       </c>
       <c r="G25" s="3" t="n">
-        <v>45627</v>
+        <v>45657</v>
+      </c>
+      <c r="H25" t="n">
+        <v>4</v>
+      </c>
+      <c r="I25" t="n">
+        <v>-2.449293598294706e-16</v>
+      </c>
+      <c r="J25" t="n">
+        <v>1</v>
+      </c>
+      <c r="K25" t="n">
+        <v>52636</v>
+      </c>
+      <c r="L25" t="n">
+        <v>30882</v>
+      </c>
+      <c r="M25" t="n">
+        <v>218995</v>
+      </c>
+      <c r="N25" t="n">
+        <v>45981.33333333334</v>
+      </c>
+      <c r="O25" t="n">
+        <v>72584.66666666667</v>
+      </c>
+      <c r="P25" t="n">
+        <v>378</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>327</v>
+      </c>
+      <c r="R25" t="n">
+        <v>391.3333333333333</v>
+      </c>
+      <c r="S25" t="n">
+        <v>25</v>
+      </c>
+      <c r="T25" t="n">
+        <v>23</v>
       </c>
     </row>
     <row r="26">
@@ -1085,7 +2032,7 @@
         <v>1</v>
       </c>
       <c r="D26" s="2" t="n">
-        <v>45658</v>
+        <v>45688</v>
       </c>
       <c r="E26" t="n">
         <v>42550</v>
@@ -1094,7 +2041,46 @@
         <v>481</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>45658</v>
+        <v>45688</v>
+      </c>
+      <c r="H26" t="n">
+        <v>1</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0.4999999999999999</v>
+      </c>
+      <c r="J26" t="n">
+        <v>0.8660254037844387</v>
+      </c>
+      <c r="K26" t="n">
+        <v>55407</v>
+      </c>
+      <c r="L26" t="n">
+        <v>54426</v>
+      </c>
+      <c r="M26" t="n">
+        <v>45828</v>
+      </c>
+      <c r="N26" t="n">
+        <v>54156.33333333334</v>
+      </c>
+      <c r="O26" t="n">
+        <v>45320</v>
+      </c>
+      <c r="P26" t="n">
+        <v>403</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>469</v>
+      </c>
+      <c r="R26" t="n">
+        <v>416.6666666666667</v>
+      </c>
+      <c r="S26" t="n">
+        <v>78</v>
+      </c>
+      <c r="T26" t="n">
+        <v>24</v>
       </c>
     </row>
     <row r="27">
@@ -1110,7 +2096,7 @@
         <v>2</v>
       </c>
       <c r="D27" s="2" t="n">
-        <v>45689</v>
+        <v>45716</v>
       </c>
       <c r="E27" t="n">
         <v>41988</v>
@@ -1119,7 +2105,46 @@
         <v>378</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>45689</v>
+        <v>45716</v>
+      </c>
+      <c r="H27" t="n">
+        <v>1</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0.8660254037844386</v>
+      </c>
+      <c r="J27" t="n">
+        <v>0.5000000000000001</v>
+      </c>
+      <c r="K27" t="n">
+        <v>42550</v>
+      </c>
+      <c r="L27" t="n">
+        <v>52636</v>
+      </c>
+      <c r="M27" t="n">
+        <v>32741</v>
+      </c>
+      <c r="N27" t="n">
+        <v>50197.66666666666</v>
+      </c>
+      <c r="O27" t="n">
+        <v>44773.66666666666</v>
+      </c>
+      <c r="P27" t="n">
+        <v>481</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>378</v>
+      </c>
+      <c r="R27" t="n">
+        <v>420.6666666666667</v>
+      </c>
+      <c r="S27" t="n">
+        <v>-103</v>
+      </c>
+      <c r="T27" t="n">
+        <v>25</v>
       </c>
     </row>
     <row r="28">
@@ -1135,7 +2160,7 @@
         <v>3</v>
       </c>
       <c r="D28" s="2" t="n">
-        <v>45717</v>
+        <v>45747</v>
       </c>
       <c r="E28" t="n">
         <v>48848</v>
@@ -1144,7 +2169,46 @@
         <v>348</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>45717</v>
+        <v>45747</v>
+      </c>
+      <c r="H28" t="n">
+        <v>1</v>
+      </c>
+      <c r="I28" t="n">
+        <v>1</v>
+      </c>
+      <c r="J28" t="n">
+        <v>6.123233995736766e-17</v>
+      </c>
+      <c r="K28" t="n">
+        <v>41988</v>
+      </c>
+      <c r="L28" t="n">
+        <v>55407</v>
+      </c>
+      <c r="M28" t="n">
+        <v>30882</v>
+      </c>
+      <c r="N28" t="n">
+        <v>46648.33333333334</v>
+      </c>
+      <c r="O28" t="n">
+        <v>46314.83333333334</v>
+      </c>
+      <c r="P28" t="n">
+        <v>378</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>403</v>
+      </c>
+      <c r="R28" t="n">
+        <v>420.6666666666667</v>
+      </c>
+      <c r="S28" t="n">
+        <v>-30</v>
+      </c>
+      <c r="T28" t="n">
+        <v>26</v>
       </c>
     </row>
     <row r="29">
@@ -1160,7 +2224,7 @@
         <v>4</v>
       </c>
       <c r="D29" s="2" t="n">
-        <v>45748</v>
+        <v>45777</v>
       </c>
       <c r="E29" t="n">
         <v>51618</v>
@@ -1169,7 +2233,46 @@
         <v>397</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>45748</v>
+        <v>45777</v>
+      </c>
+      <c r="H29" t="n">
+        <v>2</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0.8660254037844387</v>
+      </c>
+      <c r="J29" t="n">
+        <v>-0.4999999999999998</v>
+      </c>
+      <c r="K29" t="n">
+        <v>48848</v>
+      </c>
+      <c r="L29" t="n">
+        <v>42550</v>
+      </c>
+      <c r="M29" t="n">
+        <v>54426</v>
+      </c>
+      <c r="N29" t="n">
+        <v>44462</v>
+      </c>
+      <c r="O29" t="n">
+        <v>49309.16666666666</v>
+      </c>
+      <c r="P29" t="n">
+        <v>348</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>481</v>
+      </c>
+      <c r="R29" t="n">
+        <v>402.3333333333333</v>
+      </c>
+      <c r="S29" t="n">
+        <v>49</v>
+      </c>
+      <c r="T29" t="n">
+        <v>27</v>
       </c>
     </row>
     <row r="30">
@@ -1185,7 +2288,7 @@
         <v>5</v>
       </c>
       <c r="D30" s="2" t="n">
-        <v>45778</v>
+        <v>45808</v>
       </c>
       <c r="E30" t="n">
         <v>52700</v>
@@ -1194,7 +2297,46 @@
         <v>360</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>45778</v>
+        <v>45808</v>
+      </c>
+      <c r="H30" t="n">
+        <v>2</v>
+      </c>
+      <c r="I30" t="n">
+        <v>0.4999999999999999</v>
+      </c>
+      <c r="J30" t="n">
+        <v>-0.8660254037844387</v>
+      </c>
+      <c r="K30" t="n">
+        <v>51618</v>
+      </c>
+      <c r="L30" t="n">
+        <v>41988</v>
+      </c>
+      <c r="M30" t="n">
+        <v>52636</v>
+      </c>
+      <c r="N30" t="n">
+        <v>47484.66666666666</v>
+      </c>
+      <c r="O30" t="n">
+        <v>48841.16666666666</v>
+      </c>
+      <c r="P30" t="n">
+        <v>397</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>378</v>
+      </c>
+      <c r="R30" t="n">
+        <v>374.3333333333333</v>
+      </c>
+      <c r="S30" t="n">
+        <v>-37</v>
+      </c>
+      <c r="T30" t="n">
+        <v>28</v>
       </c>
     </row>
     <row r="31">
@@ -1210,7 +2352,7 @@
         <v>6</v>
       </c>
       <c r="D31" s="2" t="n">
-        <v>45809</v>
+        <v>45838</v>
       </c>
       <c r="E31" t="n">
         <v>35302</v>
@@ -1219,7 +2361,46 @@
         <v>278</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>45809</v>
+        <v>45838</v>
+      </c>
+      <c r="H31" t="n">
+        <v>2</v>
+      </c>
+      <c r="I31" t="n">
+        <v>1.224646799147353e-16</v>
+      </c>
+      <c r="J31" t="n">
+        <v>-1</v>
+      </c>
+      <c r="K31" t="n">
+        <v>52700</v>
+      </c>
+      <c r="L31" t="n">
+        <v>48848</v>
+      </c>
+      <c r="M31" t="n">
+        <v>55407</v>
+      </c>
+      <c r="N31" t="n">
+        <v>51055.33333333334</v>
+      </c>
+      <c r="O31" t="n">
+        <v>48851.83333333334</v>
+      </c>
+      <c r="P31" t="n">
+        <v>360</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>348</v>
+      </c>
+      <c r="R31" t="n">
+        <v>368.3333333333333</v>
+      </c>
+      <c r="S31" t="n">
+        <v>-82</v>
+      </c>
+      <c r="T31" t="n">
+        <v>29</v>
       </c>
     </row>
     <row r="32">
@@ -1235,7 +2416,7 @@
         <v>7</v>
       </c>
       <c r="D32" s="2" t="n">
-        <v>45839</v>
+        <v>45869</v>
       </c>
       <c r="E32" t="n">
         <v>27572</v>
@@ -1244,7 +2425,46 @@
         <v>267</v>
       </c>
       <c r="G32" s="3" t="n">
-        <v>45839</v>
+        <v>45869</v>
+      </c>
+      <c r="H32" t="n">
+        <v>3</v>
+      </c>
+      <c r="I32" t="n">
+        <v>-0.4999999999999997</v>
+      </c>
+      <c r="J32" t="n">
+        <v>-0.8660254037844388</v>
+      </c>
+      <c r="K32" t="n">
+        <v>35302</v>
+      </c>
+      <c r="L32" t="n">
+        <v>51618</v>
+      </c>
+      <c r="M32" t="n">
+        <v>42550</v>
+      </c>
+      <c r="N32" t="n">
+        <v>46540</v>
+      </c>
+      <c r="O32" t="n">
+        <v>45501</v>
+      </c>
+      <c r="P32" t="n">
+        <v>278</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>397</v>
+      </c>
+      <c r="R32" t="n">
+        <v>345</v>
+      </c>
+      <c r="S32" t="n">
+        <v>-11</v>
+      </c>
+      <c r="T32" t="n">
+        <v>30</v>
       </c>
     </row>
     <row r="33">
@@ -1260,7 +2480,7 @@
         <v>8</v>
       </c>
       <c r="D33" s="2" t="n">
-        <v>45870</v>
+        <v>45900</v>
       </c>
       <c r="E33" t="n">
         <v>27655</v>
@@ -1269,7 +2489,46 @@
         <v>256</v>
       </c>
       <c r="G33" s="3" t="n">
-        <v>45870</v>
+        <v>45900</v>
+      </c>
+      <c r="H33" t="n">
+        <v>3</v>
+      </c>
+      <c r="I33" t="n">
+        <v>-0.8660254037844385</v>
+      </c>
+      <c r="J33" t="n">
+        <v>-0.5000000000000004</v>
+      </c>
+      <c r="K33" t="n">
+        <v>27572</v>
+      </c>
+      <c r="L33" t="n">
+        <v>52700</v>
+      </c>
+      <c r="M33" t="n">
+        <v>41988</v>
+      </c>
+      <c r="N33" t="n">
+        <v>38524.66666666666</v>
+      </c>
+      <c r="O33" t="n">
+        <v>43004.66666666666</v>
+      </c>
+      <c r="P33" t="n">
+        <v>267</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>360</v>
+      </c>
+      <c r="R33" t="n">
+        <v>301.6666666666667</v>
+      </c>
+      <c r="S33" t="n">
+        <v>-11</v>
+      </c>
+      <c r="T33" t="n">
+        <v>31</v>
       </c>
     </row>
     <row r="34">
@@ -1285,7 +2544,7 @@
         <v>9</v>
       </c>
       <c r="D34" s="2" t="n">
-        <v>45901</v>
+        <v>45930</v>
       </c>
       <c r="E34" t="n">
         <v>36561</v>
@@ -1294,7 +2553,46 @@
         <v>355</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>45901</v>
+        <v>45930</v>
+      </c>
+      <c r="H34" t="n">
+        <v>3</v>
+      </c>
+      <c r="I34" t="n">
+        <v>-1</v>
+      </c>
+      <c r="J34" t="n">
+        <v>-1.83697019872103e-16</v>
+      </c>
+      <c r="K34" t="n">
+        <v>27655</v>
+      </c>
+      <c r="L34" t="n">
+        <v>35302</v>
+      </c>
+      <c r="M34" t="n">
+        <v>48848</v>
+      </c>
+      <c r="N34" t="n">
+        <v>30176.33333333333</v>
+      </c>
+      <c r="O34" t="n">
+        <v>40615.83333333334</v>
+      </c>
+      <c r="P34" t="n">
+        <v>256</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>278</v>
+      </c>
+      <c r="R34" t="n">
+        <v>267</v>
+      </c>
+      <c r="S34" t="n">
+        <v>99</v>
+      </c>
+      <c r="T34" t="n">
+        <v>32</v>
       </c>
     </row>
     <row r="35">
@@ -1310,7 +2608,7 @@
         <v>10</v>
       </c>
       <c r="D35" s="2" t="n">
-        <v>45931</v>
+        <v>45961</v>
       </c>
       <c r="E35" t="n">
         <v>32698</v>
@@ -1319,7 +2617,46 @@
         <v>357</v>
       </c>
       <c r="G35" s="3" t="n">
-        <v>45931</v>
+        <v>45961</v>
+      </c>
+      <c r="H35" t="n">
+        <v>4</v>
+      </c>
+      <c r="I35" t="n">
+        <v>-0.8660254037844386</v>
+      </c>
+      <c r="J35" t="n">
+        <v>0.5000000000000001</v>
+      </c>
+      <c r="K35" t="n">
+        <v>36561</v>
+      </c>
+      <c r="L35" t="n">
+        <v>27572</v>
+      </c>
+      <c r="M35" t="n">
+        <v>51618</v>
+      </c>
+      <c r="N35" t="n">
+        <v>30596</v>
+      </c>
+      <c r="O35" t="n">
+        <v>38568</v>
+      </c>
+      <c r="P35" t="n">
+        <v>355</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>267</v>
+      </c>
+      <c r="R35" t="n">
+        <v>292.6666666666667</v>
+      </c>
+      <c r="S35" t="n">
+        <v>2</v>
+      </c>
+      <c r="T35" t="n">
+        <v>33</v>
       </c>
     </row>
     <row r="36">
@@ -1335,7 +2672,7 @@
         <v>11</v>
       </c>
       <c r="D36" s="2" t="n">
-        <v>45962</v>
+        <v>45991</v>
       </c>
       <c r="E36" t="n">
         <v>33705</v>
@@ -1344,7 +2681,46 @@
         <v>364</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>45962</v>
+        <v>45991</v>
+      </c>
+      <c r="H36" t="n">
+        <v>4</v>
+      </c>
+      <c r="I36" t="n">
+        <v>-0.5000000000000004</v>
+      </c>
+      <c r="J36" t="n">
+        <v>0.8660254037844384</v>
+      </c>
+      <c r="K36" t="n">
+        <v>32698</v>
+      </c>
+      <c r="L36" t="n">
+        <v>27655</v>
+      </c>
+      <c r="M36" t="n">
+        <v>52700</v>
+      </c>
+      <c r="N36" t="n">
+        <v>32304.66666666667</v>
+      </c>
+      <c r="O36" t="n">
+        <v>35414.66666666666</v>
+      </c>
+      <c r="P36" t="n">
+        <v>357</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>256</v>
+      </c>
+      <c r="R36" t="n">
+        <v>322.6666666666667</v>
+      </c>
+      <c r="S36" t="n">
+        <v>7</v>
+      </c>
+      <c r="T36" t="n">
+        <v>34</v>
       </c>
     </row>
     <row r="37">
@@ -1360,7 +2736,7 @@
         <v>12</v>
       </c>
       <c r="D37" s="2" t="n">
-        <v>45992</v>
+        <v>46022</v>
       </c>
       <c r="E37" t="n">
         <v>32877</v>
@@ -1369,7 +2745,46 @@
         <v>328</v>
       </c>
       <c r="G37" s="3" t="n">
-        <v>45992</v>
+        <v>46022</v>
+      </c>
+      <c r="H37" t="n">
+        <v>4</v>
+      </c>
+      <c r="I37" t="n">
+        <v>-2.449293598294706e-16</v>
+      </c>
+      <c r="J37" t="n">
+        <v>1</v>
+      </c>
+      <c r="K37" t="n">
+        <v>33705</v>
+      </c>
+      <c r="L37" t="n">
+        <v>36561</v>
+      </c>
+      <c r="M37" t="n">
+        <v>35302</v>
+      </c>
+      <c r="N37" t="n">
+        <v>34321.33333333334</v>
+      </c>
+      <c r="O37" t="n">
+        <v>32248.83333333333</v>
+      </c>
+      <c r="P37" t="n">
+        <v>364</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>355</v>
+      </c>
+      <c r="R37" t="n">
+        <v>358.6666666666667</v>
+      </c>
+      <c r="S37" t="n">
+        <v>-36</v>
+      </c>
+      <c r="T37" t="n">
+        <v>35</v>
       </c>
     </row>
     <row r="38">
@@ -1385,7 +2800,7 @@
         <v>6</v>
       </c>
       <c r="D38" s="2" t="n">
-        <v>45444</v>
+        <v>45473</v>
       </c>
       <c r="E38" t="n">
         <v>1000</v>
@@ -1394,7 +2809,28 @@
         <v>1</v>
       </c>
       <c r="G38" s="3" t="n">
-        <v>45444</v>
+        <v>45473</v>
+      </c>
+      <c r="H38" t="n">
+        <v>2</v>
+      </c>
+      <c r="I38" t="n">
+        <v>1.224646799147353e-16</v>
+      </c>
+      <c r="J38" t="n">
+        <v>-1</v>
+      </c>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
+      <c r="O38" t="inlineStr"/>
+      <c r="P38" t="inlineStr"/>
+      <c r="Q38" t="inlineStr"/>
+      <c r="R38" t="inlineStr"/>
+      <c r="S38" t="inlineStr"/>
+      <c r="T38" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="39">
@@ -1410,7 +2846,7 @@
         <v>7</v>
       </c>
       <c r="D39" s="2" t="n">
-        <v>45474</v>
+        <v>45504</v>
       </c>
       <c r="E39" t="n">
         <v>1000</v>
@@ -1419,7 +2855,34 @@
         <v>1</v>
       </c>
       <c r="G39" s="3" t="n">
-        <v>45474</v>
+        <v>45504</v>
+      </c>
+      <c r="H39" t="n">
+        <v>3</v>
+      </c>
+      <c r="I39" t="n">
+        <v>-0.4999999999999997</v>
+      </c>
+      <c r="J39" t="n">
+        <v>-0.8660254037844388</v>
+      </c>
+      <c r="K39" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
+      <c r="O39" t="inlineStr"/>
+      <c r="P39" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q39" t="inlineStr"/>
+      <c r="R39" t="inlineStr"/>
+      <c r="S39" t="n">
+        <v>0</v>
+      </c>
+      <c r="T39" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="40">
@@ -1435,7 +2898,7 @@
         <v>8</v>
       </c>
       <c r="D40" s="2" t="n">
-        <v>45505</v>
+        <v>45535</v>
       </c>
       <c r="E40" t="n">
         <v>2200</v>
@@ -1444,7 +2907,34 @@
         <v>3</v>
       </c>
       <c r="G40" s="3" t="n">
-        <v>45505</v>
+        <v>45535</v>
+      </c>
+      <c r="H40" t="n">
+        <v>3</v>
+      </c>
+      <c r="I40" t="n">
+        <v>-0.8660254037844385</v>
+      </c>
+      <c r="J40" t="n">
+        <v>-0.5000000000000004</v>
+      </c>
+      <c r="K40" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
+      <c r="O40" t="inlineStr"/>
+      <c r="P40" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q40" t="inlineStr"/>
+      <c r="R40" t="inlineStr"/>
+      <c r="S40" t="n">
+        <v>2</v>
+      </c>
+      <c r="T40" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="41">
@@ -1460,7 +2950,7 @@
         <v>9</v>
       </c>
       <c r="D41" s="2" t="n">
-        <v>45536</v>
+        <v>45565</v>
       </c>
       <c r="E41" t="n">
         <v>3100</v>
@@ -1469,7 +2959,42 @@
         <v>4</v>
       </c>
       <c r="G41" s="3" t="n">
-        <v>45536</v>
+        <v>45565</v>
+      </c>
+      <c r="H41" t="n">
+        <v>3</v>
+      </c>
+      <c r="I41" t="n">
+        <v>-1</v>
+      </c>
+      <c r="J41" t="n">
+        <v>-1.83697019872103e-16</v>
+      </c>
+      <c r="K41" t="n">
+        <v>2200</v>
+      </c>
+      <c r="L41" t="n">
+        <v>1000</v>
+      </c>
+      <c r="M41" t="inlineStr"/>
+      <c r="N41" t="n">
+        <v>1400</v>
+      </c>
+      <c r="O41" t="inlineStr"/>
+      <c r="P41" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>1</v>
+      </c>
+      <c r="R41" t="n">
+        <v>1.666666666666667</v>
+      </c>
+      <c r="S41" t="n">
+        <v>1</v>
+      </c>
+      <c r="T41" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="42">
@@ -1485,7 +3010,7 @@
         <v>10</v>
       </c>
       <c r="D42" s="2" t="n">
-        <v>45566</v>
+        <v>45596</v>
       </c>
       <c r="E42" t="n">
         <v>6000</v>
@@ -1494,7 +3019,42 @@
         <v>3</v>
       </c>
       <c r="G42" s="3" t="n">
-        <v>45566</v>
+        <v>45596</v>
+      </c>
+      <c r="H42" t="n">
+        <v>4</v>
+      </c>
+      <c r="I42" t="n">
+        <v>-0.8660254037844386</v>
+      </c>
+      <c r="J42" t="n">
+        <v>0.5000000000000001</v>
+      </c>
+      <c r="K42" t="n">
+        <v>3100</v>
+      </c>
+      <c r="L42" t="n">
+        <v>1000</v>
+      </c>
+      <c r="M42" t="inlineStr"/>
+      <c r="N42" t="n">
+        <v>2100</v>
+      </c>
+      <c r="O42" t="inlineStr"/>
+      <c r="P42" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>1</v>
+      </c>
+      <c r="R42" t="n">
+        <v>2.666666666666667</v>
+      </c>
+      <c r="S42" t="n">
+        <v>-1</v>
+      </c>
+      <c r="T42" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="43">
@@ -1510,7 +3070,7 @@
         <v>11</v>
       </c>
       <c r="D43" s="2" t="n">
-        <v>45597</v>
+        <v>45626</v>
       </c>
       <c r="E43" t="n">
         <v>2000</v>
@@ -1519,7 +3079,42 @@
         <v>1</v>
       </c>
       <c r="G43" s="3" t="n">
-        <v>45597</v>
+        <v>45626</v>
+      </c>
+      <c r="H43" t="n">
+        <v>4</v>
+      </c>
+      <c r="I43" t="n">
+        <v>-0.5000000000000004</v>
+      </c>
+      <c r="J43" t="n">
+        <v>0.8660254037844384</v>
+      </c>
+      <c r="K43" t="n">
+        <v>6000</v>
+      </c>
+      <c r="L43" t="n">
+        <v>2200</v>
+      </c>
+      <c r="M43" t="inlineStr"/>
+      <c r="N43" t="n">
+        <v>3766.666666666667</v>
+      </c>
+      <c r="O43" t="inlineStr"/>
+      <c r="P43" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>3</v>
+      </c>
+      <c r="R43" t="n">
+        <v>3.333333333333333</v>
+      </c>
+      <c r="S43" t="n">
+        <v>-2</v>
+      </c>
+      <c r="T43" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="44">
@@ -1535,7 +3130,7 @@
         <v>12</v>
       </c>
       <c r="D44" s="2" t="n">
-        <v>45627</v>
+        <v>45657</v>
       </c>
       <c r="E44" t="n">
         <v>3000</v>
@@ -1544,7 +3139,46 @@
         <v>5</v>
       </c>
       <c r="G44" s="3" t="n">
-        <v>45627</v>
+        <v>45657</v>
+      </c>
+      <c r="H44" t="n">
+        <v>4</v>
+      </c>
+      <c r="I44" t="n">
+        <v>-2.449293598294706e-16</v>
+      </c>
+      <c r="J44" t="n">
+        <v>1</v>
+      </c>
+      <c r="K44" t="n">
+        <v>2000</v>
+      </c>
+      <c r="L44" t="n">
+        <v>3100</v>
+      </c>
+      <c r="M44" t="n">
+        <v>1000</v>
+      </c>
+      <c r="N44" t="n">
+        <v>3700</v>
+      </c>
+      <c r="O44" t="n">
+        <v>2550</v>
+      </c>
+      <c r="P44" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q44" t="n">
+        <v>4</v>
+      </c>
+      <c r="R44" t="n">
+        <v>2.666666666666667</v>
+      </c>
+      <c r="S44" t="n">
+        <v>4</v>
+      </c>
+      <c r="T44" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="45">
@@ -1560,7 +3194,7 @@
         <v>1</v>
       </c>
       <c r="D45" s="2" t="n">
-        <v>45658</v>
+        <v>45688</v>
       </c>
       <c r="E45" t="n">
         <v>9100</v>
@@ -1569,7 +3203,46 @@
         <v>9</v>
       </c>
       <c r="G45" s="3" t="n">
-        <v>45658</v>
+        <v>45688</v>
+      </c>
+      <c r="H45" t="n">
+        <v>1</v>
+      </c>
+      <c r="I45" t="n">
+        <v>0.4999999999999999</v>
+      </c>
+      <c r="J45" t="n">
+        <v>0.8660254037844387</v>
+      </c>
+      <c r="K45" t="n">
+        <v>3000</v>
+      </c>
+      <c r="L45" t="n">
+        <v>6000</v>
+      </c>
+      <c r="M45" t="n">
+        <v>1000</v>
+      </c>
+      <c r="N45" t="n">
+        <v>3666.666666666667</v>
+      </c>
+      <c r="O45" t="n">
+        <v>2883.333333333333</v>
+      </c>
+      <c r="P45" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>3</v>
+      </c>
+      <c r="R45" t="n">
+        <v>3</v>
+      </c>
+      <c r="S45" t="n">
+        <v>4</v>
+      </c>
+      <c r="T45" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="46">
@@ -1585,7 +3258,7 @@
         <v>2</v>
       </c>
       <c r="D46" s="2" t="n">
-        <v>45689</v>
+        <v>45716</v>
       </c>
       <c r="E46" t="n">
         <v>5000</v>
@@ -1594,7 +3267,46 @@
         <v>3</v>
       </c>
       <c r="G46" s="3" t="n">
-        <v>45689</v>
+        <v>45716</v>
+      </c>
+      <c r="H46" t="n">
+        <v>1</v>
+      </c>
+      <c r="I46" t="n">
+        <v>0.8660254037844386</v>
+      </c>
+      <c r="J46" t="n">
+        <v>0.5000000000000001</v>
+      </c>
+      <c r="K46" t="n">
+        <v>9100</v>
+      </c>
+      <c r="L46" t="n">
+        <v>2000</v>
+      </c>
+      <c r="M46" t="n">
+        <v>2200</v>
+      </c>
+      <c r="N46" t="n">
+        <v>4700</v>
+      </c>
+      <c r="O46" t="n">
+        <v>4233.333333333333</v>
+      </c>
+      <c r="P46" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>1</v>
+      </c>
+      <c r="R46" t="n">
+        <v>5</v>
+      </c>
+      <c r="S46" t="n">
+        <v>-6</v>
+      </c>
+      <c r="T46" t="n">
+        <v>8</v>
       </c>
     </row>
     <row r="47">
@@ -1610,7 +3322,7 @@
         <v>3</v>
       </c>
       <c r="D47" s="2" t="n">
-        <v>45717</v>
+        <v>45747</v>
       </c>
       <c r="E47" t="n">
         <v>2038</v>
@@ -1619,7 +3331,46 @@
         <v>2</v>
       </c>
       <c r="G47" s="3" t="n">
-        <v>45717</v>
+        <v>45747</v>
+      </c>
+      <c r="H47" t="n">
+        <v>1</v>
+      </c>
+      <c r="I47" t="n">
+        <v>1</v>
+      </c>
+      <c r="J47" t="n">
+        <v>6.123233995736766e-17</v>
+      </c>
+      <c r="K47" t="n">
+        <v>5000</v>
+      </c>
+      <c r="L47" t="n">
+        <v>3000</v>
+      </c>
+      <c r="M47" t="n">
+        <v>3100</v>
+      </c>
+      <c r="N47" t="n">
+        <v>5700</v>
+      </c>
+      <c r="O47" t="n">
+        <v>4700</v>
+      </c>
+      <c r="P47" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q47" t="n">
+        <v>5</v>
+      </c>
+      <c r="R47" t="n">
+        <v>5.666666666666667</v>
+      </c>
+      <c r="S47" t="n">
+        <v>-1</v>
+      </c>
+      <c r="T47" t="n">
+        <v>9</v>
       </c>
     </row>
     <row r="48">
@@ -1635,7 +3386,7 @@
         <v>4</v>
       </c>
       <c r="D48" s="2" t="n">
-        <v>45748</v>
+        <v>45777</v>
       </c>
       <c r="E48" t="n">
         <v>1838</v>
@@ -1644,7 +3395,46 @@
         <v>2</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>45748</v>
+        <v>45777</v>
+      </c>
+      <c r="H48" t="n">
+        <v>2</v>
+      </c>
+      <c r="I48" t="n">
+        <v>0.8660254037844387</v>
+      </c>
+      <c r="J48" t="n">
+        <v>-0.4999999999999998</v>
+      </c>
+      <c r="K48" t="n">
+        <v>2038</v>
+      </c>
+      <c r="L48" t="n">
+        <v>9100</v>
+      </c>
+      <c r="M48" t="n">
+        <v>6000</v>
+      </c>
+      <c r="N48" t="n">
+        <v>5379.333333333333</v>
+      </c>
+      <c r="O48" t="n">
+        <v>4523</v>
+      </c>
+      <c r="P48" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q48" t="n">
+        <v>9</v>
+      </c>
+      <c r="R48" t="n">
+        <v>4.666666666666667</v>
+      </c>
+      <c r="S48" t="n">
+        <v>0</v>
+      </c>
+      <c r="T48" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="49">
@@ -1660,7 +3450,7 @@
         <v>5</v>
       </c>
       <c r="D49" s="2" t="n">
-        <v>45778</v>
+        <v>45808</v>
       </c>
       <c r="E49" t="n">
         <v>6500</v>
@@ -1669,7 +3459,46 @@
         <v>5</v>
       </c>
       <c r="G49" s="3" t="n">
-        <v>45778</v>
+        <v>45808</v>
+      </c>
+      <c r="H49" t="n">
+        <v>2</v>
+      </c>
+      <c r="I49" t="n">
+        <v>0.4999999999999999</v>
+      </c>
+      <c r="J49" t="n">
+        <v>-0.8660254037844387</v>
+      </c>
+      <c r="K49" t="n">
+        <v>1838</v>
+      </c>
+      <c r="L49" t="n">
+        <v>5000</v>
+      </c>
+      <c r="M49" t="n">
+        <v>2000</v>
+      </c>
+      <c r="N49" t="n">
+        <v>2958.666666666667</v>
+      </c>
+      <c r="O49" t="n">
+        <v>3829.333333333333</v>
+      </c>
+      <c r="P49" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q49" t="n">
+        <v>3</v>
+      </c>
+      <c r="R49" t="n">
+        <v>2.333333333333333</v>
+      </c>
+      <c r="S49" t="n">
+        <v>3</v>
+      </c>
+      <c r="T49" t="n">
+        <v>11</v>
       </c>
     </row>
     <row r="50">
@@ -1685,7 +3514,7 @@
         <v>6</v>
       </c>
       <c r="D50" s="2" t="n">
-        <v>45809</v>
+        <v>45838</v>
       </c>
       <c r="E50" t="n">
         <v>4100</v>
@@ -1694,7 +3523,46 @@
         <v>4</v>
       </c>
       <c r="G50" s="3" t="n">
-        <v>45809</v>
+        <v>45838</v>
+      </c>
+      <c r="H50" t="n">
+        <v>2</v>
+      </c>
+      <c r="I50" t="n">
+        <v>1.224646799147353e-16</v>
+      </c>
+      <c r="J50" t="n">
+        <v>-1</v>
+      </c>
+      <c r="K50" t="n">
+        <v>6500</v>
+      </c>
+      <c r="L50" t="n">
+        <v>2038</v>
+      </c>
+      <c r="M50" t="n">
+        <v>3000</v>
+      </c>
+      <c r="N50" t="n">
+        <v>3458.666666666667</v>
+      </c>
+      <c r="O50" t="n">
+        <v>4579.333333333333</v>
+      </c>
+      <c r="P50" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q50" t="n">
+        <v>2</v>
+      </c>
+      <c r="R50" t="n">
+        <v>3</v>
+      </c>
+      <c r="S50" t="n">
+        <v>-1</v>
+      </c>
+      <c r="T50" t="n">
+        <v>12</v>
       </c>
     </row>
     <row r="51">
@@ -1710,7 +3578,7 @@
         <v>7</v>
       </c>
       <c r="D51" s="2" t="n">
-        <v>45839</v>
+        <v>45869</v>
       </c>
       <c r="E51" t="n">
         <v>4409</v>
@@ -1719,7 +3587,46 @@
         <v>4</v>
       </c>
       <c r="G51" s="3" t="n">
-        <v>45839</v>
+        <v>45869</v>
+      </c>
+      <c r="H51" t="n">
+        <v>3</v>
+      </c>
+      <c r="I51" t="n">
+        <v>-0.4999999999999997</v>
+      </c>
+      <c r="J51" t="n">
+        <v>-0.8660254037844388</v>
+      </c>
+      <c r="K51" t="n">
+        <v>4100</v>
+      </c>
+      <c r="L51" t="n">
+        <v>1838</v>
+      </c>
+      <c r="M51" t="n">
+        <v>9100</v>
+      </c>
+      <c r="N51" t="n">
+        <v>4146</v>
+      </c>
+      <c r="O51" t="n">
+        <v>4762.666666666667</v>
+      </c>
+      <c r="P51" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q51" t="n">
+        <v>2</v>
+      </c>
+      <c r="R51" t="n">
+        <v>3.666666666666667</v>
+      </c>
+      <c r="S51" t="n">
+        <v>0</v>
+      </c>
+      <c r="T51" t="n">
+        <v>13</v>
       </c>
     </row>
     <row r="52">
@@ -1735,7 +3642,7 @@
         <v>8</v>
       </c>
       <c r="D52" s="2" t="n">
-        <v>45870</v>
+        <v>45900</v>
       </c>
       <c r="E52" t="n">
         <v>2728</v>
@@ -1744,7 +3651,46 @@
         <v>4</v>
       </c>
       <c r="G52" s="3" t="n">
-        <v>45870</v>
+        <v>45900</v>
+      </c>
+      <c r="H52" t="n">
+        <v>3</v>
+      </c>
+      <c r="I52" t="n">
+        <v>-0.8660254037844385</v>
+      </c>
+      <c r="J52" t="n">
+        <v>-0.5000000000000004</v>
+      </c>
+      <c r="K52" t="n">
+        <v>4409</v>
+      </c>
+      <c r="L52" t="n">
+        <v>6500</v>
+      </c>
+      <c r="M52" t="n">
+        <v>5000</v>
+      </c>
+      <c r="N52" t="n">
+        <v>5003</v>
+      </c>
+      <c r="O52" t="n">
+        <v>3980.833333333333</v>
+      </c>
+      <c r="P52" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q52" t="n">
+        <v>5</v>
+      </c>
+      <c r="R52" t="n">
+        <v>4.333333333333333</v>
+      </c>
+      <c r="S52" t="n">
+        <v>0</v>
+      </c>
+      <c r="T52" t="n">
+        <v>14</v>
       </c>
     </row>
     <row r="53">
@@ -1760,7 +3706,7 @@
         <v>9</v>
       </c>
       <c r="D53" s="2" t="n">
-        <v>45901</v>
+        <v>45930</v>
       </c>
       <c r="E53" t="n">
         <v>2000</v>
@@ -1769,7 +3715,46 @@
         <v>2</v>
       </c>
       <c r="G53" s="3" t="n">
-        <v>45901</v>
+        <v>45930</v>
+      </c>
+      <c r="H53" t="n">
+        <v>3</v>
+      </c>
+      <c r="I53" t="n">
+        <v>-1</v>
+      </c>
+      <c r="J53" t="n">
+        <v>-1.83697019872103e-16</v>
+      </c>
+      <c r="K53" t="n">
+        <v>2728</v>
+      </c>
+      <c r="L53" t="n">
+        <v>4100</v>
+      </c>
+      <c r="M53" t="n">
+        <v>2038</v>
+      </c>
+      <c r="N53" t="n">
+        <v>3745.666666666667</v>
+      </c>
+      <c r="O53" t="n">
+        <v>3602.166666666667</v>
+      </c>
+      <c r="P53" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q53" t="n">
+        <v>4</v>
+      </c>
+      <c r="R53" t="n">
+        <v>4</v>
+      </c>
+      <c r="S53" t="n">
+        <v>-2</v>
+      </c>
+      <c r="T53" t="n">
+        <v>15</v>
       </c>
     </row>
     <row r="54">
@@ -1785,7 +3770,7 @@
         <v>10</v>
       </c>
       <c r="D54" s="2" t="n">
-        <v>45931</v>
+        <v>45961</v>
       </c>
       <c r="E54" t="n">
         <v>3000</v>
@@ -1794,7 +3779,46 @@
         <v>2</v>
       </c>
       <c r="G54" s="3" t="n">
-        <v>45931</v>
+        <v>45961</v>
+      </c>
+      <c r="H54" t="n">
+        <v>4</v>
+      </c>
+      <c r="I54" t="n">
+        <v>-0.8660254037844386</v>
+      </c>
+      <c r="J54" t="n">
+        <v>0.5000000000000001</v>
+      </c>
+      <c r="K54" t="n">
+        <v>2000</v>
+      </c>
+      <c r="L54" t="n">
+        <v>4409</v>
+      </c>
+      <c r="M54" t="n">
+        <v>1838</v>
+      </c>
+      <c r="N54" t="n">
+        <v>3045.666666666667</v>
+      </c>
+      <c r="O54" t="n">
+        <v>3595.833333333333</v>
+      </c>
+      <c r="P54" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q54" t="n">
+        <v>4</v>
+      </c>
+      <c r="R54" t="n">
+        <v>3.333333333333333</v>
+      </c>
+      <c r="S54" t="n">
+        <v>0</v>
+      </c>
+      <c r="T54" t="n">
+        <v>16</v>
       </c>
     </row>
     <row r="55">
@@ -1810,7 +3834,7 @@
         <v>11</v>
       </c>
       <c r="D55" s="2" t="n">
-        <v>45962</v>
+        <v>45991</v>
       </c>
       <c r="E55" t="n">
         <v>3831</v>
@@ -1819,7 +3843,46 @@
         <v>4</v>
       </c>
       <c r="G55" s="3" t="n">
-        <v>45962</v>
+        <v>45991</v>
+      </c>
+      <c r="H55" t="n">
+        <v>4</v>
+      </c>
+      <c r="I55" t="n">
+        <v>-0.5000000000000004</v>
+      </c>
+      <c r="J55" t="n">
+        <v>0.8660254037844384</v>
+      </c>
+      <c r="K55" t="n">
+        <v>3000</v>
+      </c>
+      <c r="L55" t="n">
+        <v>2728</v>
+      </c>
+      <c r="M55" t="n">
+        <v>6500</v>
+      </c>
+      <c r="N55" t="n">
+        <v>2576</v>
+      </c>
+      <c r="O55" t="n">
+        <v>3789.5</v>
+      </c>
+      <c r="P55" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q55" t="n">
+        <v>4</v>
+      </c>
+      <c r="R55" t="n">
+        <v>2.666666666666667</v>
+      </c>
+      <c r="S55" t="n">
+        <v>2</v>
+      </c>
+      <c r="T55" t="n">
+        <v>17</v>
       </c>
     </row>
     <row r="56">
@@ -1835,7 +3898,7 @@
         <v>12</v>
       </c>
       <c r="D56" s="2" t="n">
-        <v>45992</v>
+        <v>46022</v>
       </c>
       <c r="E56" t="n">
         <v>3647</v>
@@ -1844,7 +3907,46 @@
         <v>3</v>
       </c>
       <c r="G56" s="3" t="n">
-        <v>45992</v>
+        <v>46022</v>
+      </c>
+      <c r="H56" t="n">
+        <v>4</v>
+      </c>
+      <c r="I56" t="n">
+        <v>-2.449293598294706e-16</v>
+      </c>
+      <c r="J56" t="n">
+        <v>1</v>
+      </c>
+      <c r="K56" t="n">
+        <v>3831</v>
+      </c>
+      <c r="L56" t="n">
+        <v>2000</v>
+      </c>
+      <c r="M56" t="n">
+        <v>4100</v>
+      </c>
+      <c r="N56" t="n">
+        <v>2943.666666666667</v>
+      </c>
+      <c r="O56" t="n">
+        <v>3344.666666666667</v>
+      </c>
+      <c r="P56" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q56" t="n">
+        <v>2</v>
+      </c>
+      <c r="R56" t="n">
+        <v>2.666666666666667</v>
+      </c>
+      <c r="S56" t="n">
+        <v>-1</v>
+      </c>
+      <c r="T56" t="n">
+        <v>18</v>
       </c>
     </row>
     <row r="57">
@@ -1860,7 +3962,7 @@
         <v>1</v>
       </c>
       <c r="D57" s="2" t="n">
-        <v>44927</v>
+        <v>44957</v>
       </c>
       <c r="E57" t="n">
         <v>19177</v>
@@ -1869,7 +3971,28 @@
         <v>73</v>
       </c>
       <c r="G57" s="3" t="n">
-        <v>44927</v>
+        <v>44957</v>
+      </c>
+      <c r="H57" t="n">
+        <v>1</v>
+      </c>
+      <c r="I57" t="n">
+        <v>0.4999999999999999</v>
+      </c>
+      <c r="J57" t="n">
+        <v>0.8660254037844387</v>
+      </c>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
+      <c r="M57" t="inlineStr"/>
+      <c r="N57" t="inlineStr"/>
+      <c r="O57" t="inlineStr"/>
+      <c r="P57" t="inlineStr"/>
+      <c r="Q57" t="inlineStr"/>
+      <c r="R57" t="inlineStr"/>
+      <c r="S57" t="inlineStr"/>
+      <c r="T57" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="58">
@@ -1885,7 +4008,7 @@
         <v>2</v>
       </c>
       <c r="D58" s="2" t="n">
-        <v>44958</v>
+        <v>44985</v>
       </c>
       <c r="E58" t="n">
         <v>32832</v>
@@ -1894,7 +4017,34 @@
         <v>85</v>
       </c>
       <c r="G58" s="3" t="n">
-        <v>44958</v>
+        <v>44985</v>
+      </c>
+      <c r="H58" t="n">
+        <v>1</v>
+      </c>
+      <c r="I58" t="n">
+        <v>0.8660254037844386</v>
+      </c>
+      <c r="J58" t="n">
+        <v>0.5000000000000001</v>
+      </c>
+      <c r="K58" t="n">
+        <v>19177</v>
+      </c>
+      <c r="L58" t="inlineStr"/>
+      <c r="M58" t="inlineStr"/>
+      <c r="N58" t="inlineStr"/>
+      <c r="O58" t="inlineStr"/>
+      <c r="P58" t="n">
+        <v>73</v>
+      </c>
+      <c r="Q58" t="inlineStr"/>
+      <c r="R58" t="inlineStr"/>
+      <c r="S58" t="n">
+        <v>12</v>
+      </c>
+      <c r="T58" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="59">
@@ -1910,7 +4060,7 @@
         <v>3</v>
       </c>
       <c r="D59" s="2" t="n">
-        <v>44986</v>
+        <v>45016</v>
       </c>
       <c r="E59" t="n">
         <v>30783</v>
@@ -1919,7 +4069,34 @@
         <v>97</v>
       </c>
       <c r="G59" s="3" t="n">
-        <v>44986</v>
+        <v>45016</v>
+      </c>
+      <c r="H59" t="n">
+        <v>1</v>
+      </c>
+      <c r="I59" t="n">
+        <v>1</v>
+      </c>
+      <c r="J59" t="n">
+        <v>6.123233995736766e-17</v>
+      </c>
+      <c r="K59" t="n">
+        <v>32832</v>
+      </c>
+      <c r="L59" t="inlineStr"/>
+      <c r="M59" t="inlineStr"/>
+      <c r="N59" t="inlineStr"/>
+      <c r="O59" t="inlineStr"/>
+      <c r="P59" t="n">
+        <v>85</v>
+      </c>
+      <c r="Q59" t="inlineStr"/>
+      <c r="R59" t="inlineStr"/>
+      <c r="S59" t="n">
+        <v>12</v>
+      </c>
+      <c r="T59" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="60">
@@ -1935,7 +4112,7 @@
         <v>4</v>
       </c>
       <c r="D60" s="2" t="n">
-        <v>45017</v>
+        <v>45046</v>
       </c>
       <c r="E60" t="n">
         <v>27746</v>
@@ -1944,7 +4121,42 @@
         <v>81</v>
       </c>
       <c r="G60" s="3" t="n">
-        <v>45017</v>
+        <v>45046</v>
+      </c>
+      <c r="H60" t="n">
+        <v>2</v>
+      </c>
+      <c r="I60" t="n">
+        <v>0.8660254037844387</v>
+      </c>
+      <c r="J60" t="n">
+        <v>-0.4999999999999998</v>
+      </c>
+      <c r="K60" t="n">
+        <v>30783</v>
+      </c>
+      <c r="L60" t="n">
+        <v>19177</v>
+      </c>
+      <c r="M60" t="inlineStr"/>
+      <c r="N60" t="n">
+        <v>27597.33333333333</v>
+      </c>
+      <c r="O60" t="inlineStr"/>
+      <c r="P60" t="n">
+        <v>97</v>
+      </c>
+      <c r="Q60" t="n">
+        <v>73</v>
+      </c>
+      <c r="R60" t="n">
+        <v>85</v>
+      </c>
+      <c r="S60" t="n">
+        <v>-16</v>
+      </c>
+      <c r="T60" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="61">
@@ -1960,7 +4172,7 @@
         <v>5</v>
       </c>
       <c r="D61" s="2" t="n">
-        <v>45047</v>
+        <v>45077</v>
       </c>
       <c r="E61" t="n">
         <v>30407</v>
@@ -1969,7 +4181,42 @@
         <v>81</v>
       </c>
       <c r="G61" s="3" t="n">
-        <v>45047</v>
+        <v>45077</v>
+      </c>
+      <c r="H61" t="n">
+        <v>2</v>
+      </c>
+      <c r="I61" t="n">
+        <v>0.4999999999999999</v>
+      </c>
+      <c r="J61" t="n">
+        <v>-0.8660254037844387</v>
+      </c>
+      <c r="K61" t="n">
+        <v>27746</v>
+      </c>
+      <c r="L61" t="n">
+        <v>32832</v>
+      </c>
+      <c r="M61" t="inlineStr"/>
+      <c r="N61" t="n">
+        <v>30453.66666666667</v>
+      </c>
+      <c r="O61" t="inlineStr"/>
+      <c r="P61" t="n">
+        <v>81</v>
+      </c>
+      <c r="Q61" t="n">
+        <v>85</v>
+      </c>
+      <c r="R61" t="n">
+        <v>87.66666666666667</v>
+      </c>
+      <c r="S61" t="n">
+        <v>0</v>
+      </c>
+      <c r="T61" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="62">
@@ -1985,7 +4232,7 @@
         <v>6</v>
       </c>
       <c r="D62" s="2" t="n">
-        <v>45078</v>
+        <v>45107</v>
       </c>
       <c r="E62" t="n">
         <v>18172</v>
@@ -1994,7 +4241,42 @@
         <v>50</v>
       </c>
       <c r="G62" s="3" t="n">
-        <v>45078</v>
+        <v>45107</v>
+      </c>
+      <c r="H62" t="n">
+        <v>2</v>
+      </c>
+      <c r="I62" t="n">
+        <v>1.224646799147353e-16</v>
+      </c>
+      <c r="J62" t="n">
+        <v>-1</v>
+      </c>
+      <c r="K62" t="n">
+        <v>30407</v>
+      </c>
+      <c r="L62" t="n">
+        <v>30783</v>
+      </c>
+      <c r="M62" t="inlineStr"/>
+      <c r="N62" t="n">
+        <v>29645.33333333333</v>
+      </c>
+      <c r="O62" t="inlineStr"/>
+      <c r="P62" t="n">
+        <v>81</v>
+      </c>
+      <c r="Q62" t="n">
+        <v>97</v>
+      </c>
+      <c r="R62" t="n">
+        <v>86.33333333333333</v>
+      </c>
+      <c r="S62" t="n">
+        <v>-31</v>
+      </c>
+      <c r="T62" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="63">
@@ -2010,7 +4292,7 @@
         <v>7</v>
       </c>
       <c r="D63" s="2" t="n">
-        <v>45108</v>
+        <v>45138</v>
       </c>
       <c r="E63" t="n">
         <v>23193</v>
@@ -2019,7 +4301,46 @@
         <v>61</v>
       </c>
       <c r="G63" s="3" t="n">
-        <v>45108</v>
+        <v>45138</v>
+      </c>
+      <c r="H63" t="n">
+        <v>3</v>
+      </c>
+      <c r="I63" t="n">
+        <v>-0.4999999999999997</v>
+      </c>
+      <c r="J63" t="n">
+        <v>-0.8660254037844388</v>
+      </c>
+      <c r="K63" t="n">
+        <v>18172</v>
+      </c>
+      <c r="L63" t="n">
+        <v>27746</v>
+      </c>
+      <c r="M63" t="n">
+        <v>19177</v>
+      </c>
+      <c r="N63" t="n">
+        <v>25441.66666666667</v>
+      </c>
+      <c r="O63" t="n">
+        <v>26519.5</v>
+      </c>
+      <c r="P63" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q63" t="n">
+        <v>81</v>
+      </c>
+      <c r="R63" t="n">
+        <v>70.66666666666667</v>
+      </c>
+      <c r="S63" t="n">
+        <v>11</v>
+      </c>
+      <c r="T63" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="64">
@@ -2035,7 +4356,7 @@
         <v>8</v>
       </c>
       <c r="D64" s="2" t="n">
-        <v>45139</v>
+        <v>45169</v>
       </c>
       <c r="E64" t="n">
         <v>23339</v>
@@ -2044,7 +4365,46 @@
         <v>68</v>
       </c>
       <c r="G64" s="3" t="n">
-        <v>45139</v>
+        <v>45169</v>
+      </c>
+      <c r="H64" t="n">
+        <v>3</v>
+      </c>
+      <c r="I64" t="n">
+        <v>-0.8660254037844385</v>
+      </c>
+      <c r="J64" t="n">
+        <v>-0.5000000000000004</v>
+      </c>
+      <c r="K64" t="n">
+        <v>23193</v>
+      </c>
+      <c r="L64" t="n">
+        <v>30407</v>
+      </c>
+      <c r="M64" t="n">
+        <v>32832</v>
+      </c>
+      <c r="N64" t="n">
+        <v>23924</v>
+      </c>
+      <c r="O64" t="n">
+        <v>27188.83333333333</v>
+      </c>
+      <c r="P64" t="n">
+        <v>61</v>
+      </c>
+      <c r="Q64" t="n">
+        <v>81</v>
+      </c>
+      <c r="R64" t="n">
+        <v>64</v>
+      </c>
+      <c r="S64" t="n">
+        <v>7</v>
+      </c>
+      <c r="T64" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="65">
@@ -2060,7 +4420,7 @@
         <v>9</v>
       </c>
       <c r="D65" s="2" t="n">
-        <v>45170</v>
+        <v>45199</v>
       </c>
       <c r="E65" t="n">
         <v>18175</v>
@@ -2069,7 +4429,46 @@
         <v>69</v>
       </c>
       <c r="G65" s="3" t="n">
-        <v>45170</v>
+        <v>45199</v>
+      </c>
+      <c r="H65" t="n">
+        <v>3</v>
+      </c>
+      <c r="I65" t="n">
+        <v>-1</v>
+      </c>
+      <c r="J65" t="n">
+        <v>-1.83697019872103e-16</v>
+      </c>
+      <c r="K65" t="n">
+        <v>23339</v>
+      </c>
+      <c r="L65" t="n">
+        <v>18172</v>
+      </c>
+      <c r="M65" t="n">
+        <v>30783</v>
+      </c>
+      <c r="N65" t="n">
+        <v>21568</v>
+      </c>
+      <c r="O65" t="n">
+        <v>25606.66666666667</v>
+      </c>
+      <c r="P65" t="n">
+        <v>68</v>
+      </c>
+      <c r="Q65" t="n">
+        <v>50</v>
+      </c>
+      <c r="R65" t="n">
+        <v>59.66666666666666</v>
+      </c>
+      <c r="S65" t="n">
+        <v>1</v>
+      </c>
+      <c r="T65" t="n">
+        <v>8</v>
       </c>
     </row>
     <row r="66">
@@ -2085,7 +4484,7 @@
         <v>10</v>
       </c>
       <c r="D66" s="2" t="n">
-        <v>45200</v>
+        <v>45230</v>
       </c>
       <c r="E66" t="n">
         <v>31086</v>
@@ -2094,7 +4493,46 @@
         <v>112</v>
       </c>
       <c r="G66" s="3" t="n">
-        <v>45200</v>
+        <v>45230</v>
+      </c>
+      <c r="H66" t="n">
+        <v>4</v>
+      </c>
+      <c r="I66" t="n">
+        <v>-0.8660254037844386</v>
+      </c>
+      <c r="J66" t="n">
+        <v>0.5000000000000001</v>
+      </c>
+      <c r="K66" t="n">
+        <v>18175</v>
+      </c>
+      <c r="L66" t="n">
+        <v>23193</v>
+      </c>
+      <c r="M66" t="n">
+        <v>27746</v>
+      </c>
+      <c r="N66" t="n">
+        <v>21569</v>
+      </c>
+      <c r="O66" t="n">
+        <v>23505.33333333333</v>
+      </c>
+      <c r="P66" t="n">
+        <v>69</v>
+      </c>
+      <c r="Q66" t="n">
+        <v>61</v>
+      </c>
+      <c r="R66" t="n">
+        <v>66</v>
+      </c>
+      <c r="S66" t="n">
+        <v>43</v>
+      </c>
+      <c r="T66" t="n">
+        <v>9</v>
       </c>
     </row>
     <row r="67">
@@ -2110,7 +4548,7 @@
         <v>11</v>
       </c>
       <c r="D67" s="2" t="n">
-        <v>45231</v>
+        <v>45260</v>
       </c>
       <c r="E67" t="n">
         <v>29315</v>
@@ -2119,7 +4557,46 @@
         <v>91</v>
       </c>
       <c r="G67" s="3" t="n">
-        <v>45231</v>
+        <v>45260</v>
+      </c>
+      <c r="H67" t="n">
+        <v>4</v>
+      </c>
+      <c r="I67" t="n">
+        <v>-0.5000000000000004</v>
+      </c>
+      <c r="J67" t="n">
+        <v>0.8660254037844384</v>
+      </c>
+      <c r="K67" t="n">
+        <v>31086</v>
+      </c>
+      <c r="L67" t="n">
+        <v>23339</v>
+      </c>
+      <c r="M67" t="n">
+        <v>30407</v>
+      </c>
+      <c r="N67" t="n">
+        <v>24200</v>
+      </c>
+      <c r="O67" t="n">
+        <v>24062</v>
+      </c>
+      <c r="P67" t="n">
+        <v>112</v>
+      </c>
+      <c r="Q67" t="n">
+        <v>68</v>
+      </c>
+      <c r="R67" t="n">
+        <v>83</v>
+      </c>
+      <c r="S67" t="n">
+        <v>-21</v>
+      </c>
+      <c r="T67" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="68">
@@ -2135,7 +4612,7 @@
         <v>12</v>
       </c>
       <c r="D68" s="2" t="n">
-        <v>45261</v>
+        <v>45291</v>
       </c>
       <c r="E68" t="n">
         <v>22138</v>
@@ -2144,7 +4621,46 @@
         <v>77</v>
       </c>
       <c r="G68" s="3" t="n">
-        <v>45261</v>
+        <v>45291</v>
+      </c>
+      <c r="H68" t="n">
+        <v>4</v>
+      </c>
+      <c r="I68" t="n">
+        <v>-2.449293598294706e-16</v>
+      </c>
+      <c r="J68" t="n">
+        <v>1</v>
+      </c>
+      <c r="K68" t="n">
+        <v>29315</v>
+      </c>
+      <c r="L68" t="n">
+        <v>18175</v>
+      </c>
+      <c r="M68" t="n">
+        <v>18172</v>
+      </c>
+      <c r="N68" t="n">
+        <v>26192</v>
+      </c>
+      <c r="O68" t="n">
+        <v>23880</v>
+      </c>
+      <c r="P68" t="n">
+        <v>91</v>
+      </c>
+      <c r="Q68" t="n">
+        <v>69</v>
+      </c>
+      <c r="R68" t="n">
+        <v>90.66666666666667</v>
+      </c>
+      <c r="S68" t="n">
+        <v>-14</v>
+      </c>
+      <c r="T68" t="n">
+        <v>11</v>
       </c>
     </row>
     <row r="69">
@@ -2160,7 +4676,7 @@
         <v>1</v>
       </c>
       <c r="D69" s="2" t="n">
-        <v>45292</v>
+        <v>45322</v>
       </c>
       <c r="E69" t="n">
         <v>23837</v>
@@ -2169,7 +4685,46 @@
         <v>71</v>
       </c>
       <c r="G69" s="3" t="n">
-        <v>45292</v>
+        <v>45322</v>
+      </c>
+      <c r="H69" t="n">
+        <v>1</v>
+      </c>
+      <c r="I69" t="n">
+        <v>0.4999999999999999</v>
+      </c>
+      <c r="J69" t="n">
+        <v>0.8660254037844387</v>
+      </c>
+      <c r="K69" t="n">
+        <v>22138</v>
+      </c>
+      <c r="L69" t="n">
+        <v>31086</v>
+      </c>
+      <c r="M69" t="n">
+        <v>23193</v>
+      </c>
+      <c r="N69" t="n">
+        <v>27513</v>
+      </c>
+      <c r="O69" t="n">
+        <v>24541</v>
+      </c>
+      <c r="P69" t="n">
+        <v>77</v>
+      </c>
+      <c r="Q69" t="n">
+        <v>112</v>
+      </c>
+      <c r="R69" t="n">
+        <v>93.33333333333333</v>
+      </c>
+      <c r="S69" t="n">
+        <v>-6</v>
+      </c>
+      <c r="T69" t="n">
+        <v>12</v>
       </c>
     </row>
     <row r="70">
@@ -2185,7 +4740,7 @@
         <v>2</v>
       </c>
       <c r="D70" s="2" t="n">
-        <v>45323</v>
+        <v>45351</v>
       </c>
       <c r="E70" t="n">
         <v>29299</v>
@@ -2194,7 +4749,46 @@
         <v>87</v>
       </c>
       <c r="G70" s="3" t="n">
-        <v>45323</v>
+        <v>45351</v>
+      </c>
+      <c r="H70" t="n">
+        <v>1</v>
+      </c>
+      <c r="I70" t="n">
+        <v>0.8660254037844386</v>
+      </c>
+      <c r="J70" t="n">
+        <v>0.5000000000000001</v>
+      </c>
+      <c r="K70" t="n">
+        <v>23837</v>
+      </c>
+      <c r="L70" t="n">
+        <v>29315</v>
+      </c>
+      <c r="M70" t="n">
+        <v>23339</v>
+      </c>
+      <c r="N70" t="n">
+        <v>25096.66666666667</v>
+      </c>
+      <c r="O70" t="n">
+        <v>24648.33333333333</v>
+      </c>
+      <c r="P70" t="n">
+        <v>71</v>
+      </c>
+      <c r="Q70" t="n">
+        <v>91</v>
+      </c>
+      <c r="R70" t="n">
+        <v>79.66666666666667</v>
+      </c>
+      <c r="S70" t="n">
+        <v>16</v>
+      </c>
+      <c r="T70" t="n">
+        <v>13</v>
       </c>
     </row>
     <row r="71">
@@ -2210,7 +4804,7 @@
         <v>3</v>
       </c>
       <c r="D71" s="2" t="n">
-        <v>45352</v>
+        <v>45382</v>
       </c>
       <c r="E71" t="n">
         <v>21759</v>
@@ -2219,7 +4813,46 @@
         <v>109</v>
       </c>
       <c r="G71" s="3" t="n">
-        <v>45352</v>
+        <v>45382</v>
+      </c>
+      <c r="H71" t="n">
+        <v>1</v>
+      </c>
+      <c r="I71" t="n">
+        <v>1</v>
+      </c>
+      <c r="J71" t="n">
+        <v>6.123233995736766e-17</v>
+      </c>
+      <c r="K71" t="n">
+        <v>29299</v>
+      </c>
+      <c r="L71" t="n">
+        <v>22138</v>
+      </c>
+      <c r="M71" t="n">
+        <v>18175</v>
+      </c>
+      <c r="N71" t="n">
+        <v>25091.33333333333</v>
+      </c>
+      <c r="O71" t="n">
+        <v>25641.66666666667</v>
+      </c>
+      <c r="P71" t="n">
+        <v>87</v>
+      </c>
+      <c r="Q71" t="n">
+        <v>77</v>
+      </c>
+      <c r="R71" t="n">
+        <v>78.33333333333333</v>
+      </c>
+      <c r="S71" t="n">
+        <v>22</v>
+      </c>
+      <c r="T71" t="n">
+        <v>14</v>
       </c>
     </row>
     <row r="72">
@@ -2235,7 +4868,7 @@
         <v>4</v>
       </c>
       <c r="D72" s="2" t="n">
-        <v>45383</v>
+        <v>45412</v>
       </c>
       <c r="E72" t="n">
         <v>18289</v>
@@ -2244,7 +4877,46 @@
         <v>58</v>
       </c>
       <c r="G72" s="3" t="n">
-        <v>45383</v>
+        <v>45412</v>
+      </c>
+      <c r="H72" t="n">
+        <v>2</v>
+      </c>
+      <c r="I72" t="n">
+        <v>0.8660254037844387</v>
+      </c>
+      <c r="J72" t="n">
+        <v>-0.4999999999999998</v>
+      </c>
+      <c r="K72" t="n">
+        <v>21759</v>
+      </c>
+      <c r="L72" t="n">
+        <v>23837</v>
+      </c>
+      <c r="M72" t="n">
+        <v>31086</v>
+      </c>
+      <c r="N72" t="n">
+        <v>24965</v>
+      </c>
+      <c r="O72" t="n">
+        <v>26239</v>
+      </c>
+      <c r="P72" t="n">
+        <v>109</v>
+      </c>
+      <c r="Q72" t="n">
+        <v>71</v>
+      </c>
+      <c r="R72" t="n">
+        <v>89</v>
+      </c>
+      <c r="S72" t="n">
+        <v>-51</v>
+      </c>
+      <c r="T72" t="n">
+        <v>15</v>
       </c>
     </row>
     <row r="73">
@@ -2260,7 +4932,7 @@
         <v>5</v>
       </c>
       <c r="D73" s="2" t="n">
-        <v>45413</v>
+        <v>45443</v>
       </c>
       <c r="E73" t="n">
         <v>21506</v>
@@ -2269,7 +4941,46 @@
         <v>75</v>
       </c>
       <c r="G73" s="3" t="n">
-        <v>45413</v>
+        <v>45443</v>
+      </c>
+      <c r="H73" t="n">
+        <v>2</v>
+      </c>
+      <c r="I73" t="n">
+        <v>0.4999999999999999</v>
+      </c>
+      <c r="J73" t="n">
+        <v>-0.8660254037844387</v>
+      </c>
+      <c r="K73" t="n">
+        <v>18289</v>
+      </c>
+      <c r="L73" t="n">
+        <v>29299</v>
+      </c>
+      <c r="M73" t="n">
+        <v>29315</v>
+      </c>
+      <c r="N73" t="n">
+        <v>23115.66666666667</v>
+      </c>
+      <c r="O73" t="n">
+        <v>24106.16666666667</v>
+      </c>
+      <c r="P73" t="n">
+        <v>58</v>
+      </c>
+      <c r="Q73" t="n">
+        <v>87</v>
+      </c>
+      <c r="R73" t="n">
+        <v>84.66666666666667</v>
+      </c>
+      <c r="S73" t="n">
+        <v>17</v>
+      </c>
+      <c r="T73" t="n">
+        <v>16</v>
       </c>
     </row>
     <row r="74">
@@ -2285,7 +4996,7 @@
         <v>6</v>
       </c>
       <c r="D74" s="2" t="n">
-        <v>45444</v>
+        <v>45473</v>
       </c>
       <c r="E74" t="n">
         <v>21056</v>
@@ -2294,7 +5005,46 @@
         <v>67</v>
       </c>
       <c r="G74" s="3" t="n">
-        <v>45444</v>
+        <v>45473</v>
+      </c>
+      <c r="H74" t="n">
+        <v>2</v>
+      </c>
+      <c r="I74" t="n">
+        <v>1.224646799147353e-16</v>
+      </c>
+      <c r="J74" t="n">
+        <v>-1</v>
+      </c>
+      <c r="K74" t="n">
+        <v>21506</v>
+      </c>
+      <c r="L74" t="n">
+        <v>21759</v>
+      </c>
+      <c r="M74" t="n">
+        <v>22138</v>
+      </c>
+      <c r="N74" t="n">
+        <v>20518</v>
+      </c>
+      <c r="O74" t="n">
+        <v>22804.66666666667</v>
+      </c>
+      <c r="P74" t="n">
+        <v>75</v>
+      </c>
+      <c r="Q74" t="n">
+        <v>109</v>
+      </c>
+      <c r="R74" t="n">
+        <v>80.66666666666667</v>
+      </c>
+      <c r="S74" t="n">
+        <v>-8</v>
+      </c>
+      <c r="T74" t="n">
+        <v>17</v>
       </c>
     </row>
     <row r="75">
@@ -2310,7 +5060,7 @@
         <v>7</v>
       </c>
       <c r="D75" s="2" t="n">
-        <v>45474</v>
+        <v>45504</v>
       </c>
       <c r="E75" t="n">
         <v>21726</v>
@@ -2319,7 +5069,46 @@
         <v>113</v>
       </c>
       <c r="G75" s="3" t="n">
-        <v>45474</v>
+        <v>45504</v>
+      </c>
+      <c r="H75" t="n">
+        <v>3</v>
+      </c>
+      <c r="I75" t="n">
+        <v>-0.4999999999999997</v>
+      </c>
+      <c r="J75" t="n">
+        <v>-0.8660254037844388</v>
+      </c>
+      <c r="K75" t="n">
+        <v>21056</v>
+      </c>
+      <c r="L75" t="n">
+        <v>18289</v>
+      </c>
+      <c r="M75" t="n">
+        <v>23837</v>
+      </c>
+      <c r="N75" t="n">
+        <v>20283.66666666667</v>
+      </c>
+      <c r="O75" t="n">
+        <v>22624.33333333333</v>
+      </c>
+      <c r="P75" t="n">
+        <v>67</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>58</v>
+      </c>
+      <c r="R75" t="n">
+        <v>66.66666666666667</v>
+      </c>
+      <c r="S75" t="n">
+        <v>46</v>
+      </c>
+      <c r="T75" t="n">
+        <v>18</v>
       </c>
     </row>
     <row r="76">
@@ -2335,7 +5124,7 @@
         <v>8</v>
       </c>
       <c r="D76" s="2" t="n">
-        <v>45505</v>
+        <v>45535</v>
       </c>
       <c r="E76" t="n">
         <v>27903</v>
@@ -2344,7 +5133,46 @@
         <v>63</v>
       </c>
       <c r="G76" s="3" t="n">
-        <v>45505</v>
+        <v>45535</v>
+      </c>
+      <c r="H76" t="n">
+        <v>3</v>
+      </c>
+      <c r="I76" t="n">
+        <v>-0.8660254037844385</v>
+      </c>
+      <c r="J76" t="n">
+        <v>-0.5000000000000004</v>
+      </c>
+      <c r="K76" t="n">
+        <v>21726</v>
+      </c>
+      <c r="L76" t="n">
+        <v>21506</v>
+      </c>
+      <c r="M76" t="n">
+        <v>29299</v>
+      </c>
+      <c r="N76" t="n">
+        <v>21429.33333333333</v>
+      </c>
+      <c r="O76" t="n">
+        <v>22272.5</v>
+      </c>
+      <c r="P76" t="n">
+        <v>113</v>
+      </c>
+      <c r="Q76" t="n">
+        <v>75</v>
+      </c>
+      <c r="R76" t="n">
+        <v>85</v>
+      </c>
+      <c r="S76" t="n">
+        <v>-50</v>
+      </c>
+      <c r="T76" t="n">
+        <v>19</v>
       </c>
     </row>
     <row r="77">
@@ -2360,7 +5188,7 @@
         <v>9</v>
       </c>
       <c r="D77" s="2" t="n">
-        <v>45536</v>
+        <v>45565</v>
       </c>
       <c r="E77" t="n">
         <v>22048</v>
@@ -2369,7 +5197,46 @@
         <v>74</v>
       </c>
       <c r="G77" s="3" t="n">
-        <v>45536</v>
+        <v>45565</v>
+      </c>
+      <c r="H77" t="n">
+        <v>3</v>
+      </c>
+      <c r="I77" t="n">
+        <v>-1</v>
+      </c>
+      <c r="J77" t="n">
+        <v>-1.83697019872103e-16</v>
+      </c>
+      <c r="K77" t="n">
+        <v>27903</v>
+      </c>
+      <c r="L77" t="n">
+        <v>21056</v>
+      </c>
+      <c r="M77" t="n">
+        <v>21759</v>
+      </c>
+      <c r="N77" t="n">
+        <v>23561.66666666667</v>
+      </c>
+      <c r="O77" t="n">
+        <v>22039.83333333333</v>
+      </c>
+      <c r="P77" t="n">
+        <v>63</v>
+      </c>
+      <c r="Q77" t="n">
+        <v>67</v>
+      </c>
+      <c r="R77" t="n">
+        <v>81</v>
+      </c>
+      <c r="S77" t="n">
+        <v>11</v>
+      </c>
+      <c r="T77" t="n">
+        <v>20</v>
       </c>
     </row>
     <row r="78">
@@ -2385,7 +5252,7 @@
         <v>10</v>
       </c>
       <c r="D78" s="2" t="n">
-        <v>45566</v>
+        <v>45596</v>
       </c>
       <c r="E78" t="n">
         <v>34776</v>
@@ -2394,7 +5261,46 @@
         <v>96</v>
       </c>
       <c r="G78" s="3" t="n">
-        <v>45566</v>
+        <v>45596</v>
+      </c>
+      <c r="H78" t="n">
+        <v>4</v>
+      </c>
+      <c r="I78" t="n">
+        <v>-0.8660254037844386</v>
+      </c>
+      <c r="J78" t="n">
+        <v>0.5000000000000001</v>
+      </c>
+      <c r="K78" t="n">
+        <v>22048</v>
+      </c>
+      <c r="L78" t="n">
+        <v>21726</v>
+      </c>
+      <c r="M78" t="n">
+        <v>18289</v>
+      </c>
+      <c r="N78" t="n">
+        <v>23892.33333333333</v>
+      </c>
+      <c r="O78" t="n">
+        <v>22088</v>
+      </c>
+      <c r="P78" t="n">
+        <v>74</v>
+      </c>
+      <c r="Q78" t="n">
+        <v>113</v>
+      </c>
+      <c r="R78" t="n">
+        <v>83.33333333333333</v>
+      </c>
+      <c r="S78" t="n">
+        <v>22</v>
+      </c>
+      <c r="T78" t="n">
+        <v>21</v>
       </c>
     </row>
     <row r="79">
@@ -2410,7 +5316,7 @@
         <v>11</v>
       </c>
       <c r="D79" s="2" t="n">
-        <v>45597</v>
+        <v>45626</v>
       </c>
       <c r="E79" t="n">
         <v>17472</v>
@@ -2419,7 +5325,46 @@
         <v>58</v>
       </c>
       <c r="G79" s="3" t="n">
-        <v>45597</v>
+        <v>45626</v>
+      </c>
+      <c r="H79" t="n">
+        <v>4</v>
+      </c>
+      <c r="I79" t="n">
+        <v>-0.5000000000000004</v>
+      </c>
+      <c r="J79" t="n">
+        <v>0.8660254037844384</v>
+      </c>
+      <c r="K79" t="n">
+        <v>34776</v>
+      </c>
+      <c r="L79" t="n">
+        <v>27903</v>
+      </c>
+      <c r="M79" t="n">
+        <v>21506</v>
+      </c>
+      <c r="N79" t="n">
+        <v>28242.33333333333</v>
+      </c>
+      <c r="O79" t="n">
+        <v>24835.83333333333</v>
+      </c>
+      <c r="P79" t="n">
+        <v>96</v>
+      </c>
+      <c r="Q79" t="n">
+        <v>63</v>
+      </c>
+      <c r="R79" t="n">
+        <v>77.66666666666667</v>
+      </c>
+      <c r="S79" t="n">
+        <v>-38</v>
+      </c>
+      <c r="T79" t="n">
+        <v>22</v>
       </c>
     </row>
     <row r="80">
@@ -2435,7 +5380,7 @@
         <v>12</v>
       </c>
       <c r="D80" s="2" t="n">
-        <v>45627</v>
+        <v>45657</v>
       </c>
       <c r="E80" t="n">
         <v>32872</v>
@@ -2444,7 +5389,46 @@
         <v>91</v>
       </c>
       <c r="G80" s="3" t="n">
-        <v>45627</v>
+        <v>45657</v>
+      </c>
+      <c r="H80" t="n">
+        <v>4</v>
+      </c>
+      <c r="I80" t="n">
+        <v>-2.449293598294706e-16</v>
+      </c>
+      <c r="J80" t="n">
+        <v>1</v>
+      </c>
+      <c r="K80" t="n">
+        <v>17472</v>
+      </c>
+      <c r="L80" t="n">
+        <v>22048</v>
+      </c>
+      <c r="M80" t="n">
+        <v>21056</v>
+      </c>
+      <c r="N80" t="n">
+        <v>24765.33333333333</v>
+      </c>
+      <c r="O80" t="n">
+        <v>24163.5</v>
+      </c>
+      <c r="P80" t="n">
+        <v>58</v>
+      </c>
+      <c r="Q80" t="n">
+        <v>74</v>
+      </c>
+      <c r="R80" t="n">
+        <v>76</v>
+      </c>
+      <c r="S80" t="n">
+        <v>33</v>
+      </c>
+      <c r="T80" t="n">
+        <v>23</v>
       </c>
     </row>
     <row r="81">
@@ -2460,7 +5444,7 @@
         <v>1</v>
       </c>
       <c r="D81" s="2" t="n">
-        <v>45658</v>
+        <v>45688</v>
       </c>
       <c r="E81" t="n">
         <v>27417</v>
@@ -2469,7 +5453,46 @@
         <v>84</v>
       </c>
       <c r="G81" s="3" t="n">
-        <v>45658</v>
+        <v>45688</v>
+      </c>
+      <c r="H81" t="n">
+        <v>1</v>
+      </c>
+      <c r="I81" t="n">
+        <v>0.4999999999999999</v>
+      </c>
+      <c r="J81" t="n">
+        <v>0.8660254037844387</v>
+      </c>
+      <c r="K81" t="n">
+        <v>32872</v>
+      </c>
+      <c r="L81" t="n">
+        <v>34776</v>
+      </c>
+      <c r="M81" t="n">
+        <v>21726</v>
+      </c>
+      <c r="N81" t="n">
+        <v>28373.33333333333</v>
+      </c>
+      <c r="O81" t="n">
+        <v>26132.83333333333</v>
+      </c>
+      <c r="P81" t="n">
+        <v>91</v>
+      </c>
+      <c r="Q81" t="n">
+        <v>96</v>
+      </c>
+      <c r="R81" t="n">
+        <v>81.66666666666667</v>
+      </c>
+      <c r="S81" t="n">
+        <v>-7</v>
+      </c>
+      <c r="T81" t="n">
+        <v>24</v>
       </c>
     </row>
     <row r="82">
@@ -2485,7 +5508,7 @@
         <v>2</v>
       </c>
       <c r="D82" s="2" t="n">
-        <v>45689</v>
+        <v>45716</v>
       </c>
       <c r="E82" t="n">
         <v>22739</v>
@@ -2494,7 +5517,46 @@
         <v>78</v>
       </c>
       <c r="G82" s="3" t="n">
-        <v>45689</v>
+        <v>45716</v>
+      </c>
+      <c r="H82" t="n">
+        <v>1</v>
+      </c>
+      <c r="I82" t="n">
+        <v>0.8660254037844386</v>
+      </c>
+      <c r="J82" t="n">
+        <v>0.5000000000000001</v>
+      </c>
+      <c r="K82" t="n">
+        <v>27417</v>
+      </c>
+      <c r="L82" t="n">
+        <v>17472</v>
+      </c>
+      <c r="M82" t="n">
+        <v>27903</v>
+      </c>
+      <c r="N82" t="n">
+        <v>25920.33333333333</v>
+      </c>
+      <c r="O82" t="n">
+        <v>27081.33333333333</v>
+      </c>
+      <c r="P82" t="n">
+        <v>84</v>
+      </c>
+      <c r="Q82" t="n">
+        <v>58</v>
+      </c>
+      <c r="R82" t="n">
+        <v>77.66666666666667</v>
+      </c>
+      <c r="S82" t="n">
+        <v>-6</v>
+      </c>
+      <c r="T82" t="n">
+        <v>25</v>
       </c>
     </row>
     <row r="83">
@@ -2510,7 +5572,7 @@
         <v>3</v>
       </c>
       <c r="D83" s="2" t="n">
-        <v>45717</v>
+        <v>45747</v>
       </c>
       <c r="E83" t="n">
         <v>26385</v>
@@ -2519,7 +5581,46 @@
         <v>58</v>
       </c>
       <c r="G83" s="3" t="n">
-        <v>45717</v>
+        <v>45747</v>
+      </c>
+      <c r="H83" t="n">
+        <v>1</v>
+      </c>
+      <c r="I83" t="n">
+        <v>1</v>
+      </c>
+      <c r="J83" t="n">
+        <v>6.123233995736766e-17</v>
+      </c>
+      <c r="K83" t="n">
+        <v>22739</v>
+      </c>
+      <c r="L83" t="n">
+        <v>32872</v>
+      </c>
+      <c r="M83" t="n">
+        <v>22048</v>
+      </c>
+      <c r="N83" t="n">
+        <v>27676</v>
+      </c>
+      <c r="O83" t="n">
+        <v>26220.66666666667</v>
+      </c>
+      <c r="P83" t="n">
+        <v>78</v>
+      </c>
+      <c r="Q83" t="n">
+        <v>91</v>
+      </c>
+      <c r="R83" t="n">
+        <v>84.33333333333333</v>
+      </c>
+      <c r="S83" t="n">
+        <v>-20</v>
+      </c>
+      <c r="T83" t="n">
+        <v>26</v>
       </c>
     </row>
     <row r="84">
@@ -2535,7 +5636,7 @@
         <v>4</v>
       </c>
       <c r="D84" s="2" t="n">
-        <v>45748</v>
+        <v>45777</v>
       </c>
       <c r="E84" t="n">
         <v>28813</v>
@@ -2544,7 +5645,46 @@
         <v>91</v>
       </c>
       <c r="G84" s="3" t="n">
-        <v>45748</v>
+        <v>45777</v>
+      </c>
+      <c r="H84" t="n">
+        <v>2</v>
+      </c>
+      <c r="I84" t="n">
+        <v>0.8660254037844387</v>
+      </c>
+      <c r="J84" t="n">
+        <v>-0.4999999999999998</v>
+      </c>
+      <c r="K84" t="n">
+        <v>26385</v>
+      </c>
+      <c r="L84" t="n">
+        <v>27417</v>
+      </c>
+      <c r="M84" t="n">
+        <v>34776</v>
+      </c>
+      <c r="N84" t="n">
+        <v>25513.66666666667</v>
+      </c>
+      <c r="O84" t="n">
+        <v>26943.5</v>
+      </c>
+      <c r="P84" t="n">
+        <v>58</v>
+      </c>
+      <c r="Q84" t="n">
+        <v>84</v>
+      </c>
+      <c r="R84" t="n">
+        <v>73.33333333333333</v>
+      </c>
+      <c r="S84" t="n">
+        <v>33</v>
+      </c>
+      <c r="T84" t="n">
+        <v>27</v>
       </c>
     </row>
     <row r="85">
@@ -2560,7 +5700,7 @@
         <v>5</v>
       </c>
       <c r="D85" s="2" t="n">
-        <v>45778</v>
+        <v>45808</v>
       </c>
       <c r="E85" t="n">
         <v>30370</v>
@@ -2569,7 +5709,46 @@
         <v>83</v>
       </c>
       <c r="G85" s="3" t="n">
-        <v>45778</v>
+        <v>45808</v>
+      </c>
+      <c r="H85" t="n">
+        <v>2</v>
+      </c>
+      <c r="I85" t="n">
+        <v>0.4999999999999999</v>
+      </c>
+      <c r="J85" t="n">
+        <v>-0.8660254037844387</v>
+      </c>
+      <c r="K85" t="n">
+        <v>28813</v>
+      </c>
+      <c r="L85" t="n">
+        <v>22739</v>
+      </c>
+      <c r="M85" t="n">
+        <v>17472</v>
+      </c>
+      <c r="N85" t="n">
+        <v>25979</v>
+      </c>
+      <c r="O85" t="n">
+        <v>25949.66666666667</v>
+      </c>
+      <c r="P85" t="n">
+        <v>91</v>
+      </c>
+      <c r="Q85" t="n">
+        <v>78</v>
+      </c>
+      <c r="R85" t="n">
+        <v>75.66666666666667</v>
+      </c>
+      <c r="S85" t="n">
+        <v>-8</v>
+      </c>
+      <c r="T85" t="n">
+        <v>28</v>
       </c>
     </row>
     <row r="86">
@@ -2585,7 +5764,7 @@
         <v>6</v>
       </c>
       <c r="D86" s="2" t="n">
-        <v>45809</v>
+        <v>45838</v>
       </c>
       <c r="E86" t="n">
         <v>23965</v>
@@ -2594,7 +5773,46 @@
         <v>55</v>
       </c>
       <c r="G86" s="3" t="n">
-        <v>45809</v>
+        <v>45838</v>
+      </c>
+      <c r="H86" t="n">
+        <v>2</v>
+      </c>
+      <c r="I86" t="n">
+        <v>1.224646799147353e-16</v>
+      </c>
+      <c r="J86" t="n">
+        <v>-1</v>
+      </c>
+      <c r="K86" t="n">
+        <v>30370</v>
+      </c>
+      <c r="L86" t="n">
+        <v>26385</v>
+      </c>
+      <c r="M86" t="n">
+        <v>32872</v>
+      </c>
+      <c r="N86" t="n">
+        <v>28522.66666666667</v>
+      </c>
+      <c r="O86" t="n">
+        <v>28099.33333333333</v>
+      </c>
+      <c r="P86" t="n">
+        <v>83</v>
+      </c>
+      <c r="Q86" t="n">
+        <v>58</v>
+      </c>
+      <c r="R86" t="n">
+        <v>77.33333333333333</v>
+      </c>
+      <c r="S86" t="n">
+        <v>-28</v>
+      </c>
+      <c r="T86" t="n">
+        <v>29</v>
       </c>
     </row>
     <row r="87">
@@ -2610,7 +5828,7 @@
         <v>7</v>
       </c>
       <c r="D87" s="2" t="n">
-        <v>45839</v>
+        <v>45869</v>
       </c>
       <c r="E87" t="n">
         <v>34190</v>
@@ -2619,7 +5837,46 @@
         <v>83</v>
       </c>
       <c r="G87" s="3" t="n">
-        <v>45839</v>
+        <v>45869</v>
+      </c>
+      <c r="H87" t="n">
+        <v>3</v>
+      </c>
+      <c r="I87" t="n">
+        <v>-0.4999999999999997</v>
+      </c>
+      <c r="J87" t="n">
+        <v>-0.8660254037844388</v>
+      </c>
+      <c r="K87" t="n">
+        <v>23965</v>
+      </c>
+      <c r="L87" t="n">
+        <v>28813</v>
+      </c>
+      <c r="M87" t="n">
+        <v>27417</v>
+      </c>
+      <c r="N87" t="n">
+        <v>27716</v>
+      </c>
+      <c r="O87" t="n">
+        <v>26614.83333333333</v>
+      </c>
+      <c r="P87" t="n">
+        <v>55</v>
+      </c>
+      <c r="Q87" t="n">
+        <v>91</v>
+      </c>
+      <c r="R87" t="n">
+        <v>76.33333333333333</v>
+      </c>
+      <c r="S87" t="n">
+        <v>28</v>
+      </c>
+      <c r="T87" t="n">
+        <v>30</v>
       </c>
     </row>
     <row r="88">
@@ -2635,7 +5892,7 @@
         <v>8</v>
       </c>
       <c r="D88" s="2" t="n">
-        <v>45870</v>
+        <v>45900</v>
       </c>
       <c r="E88" t="n">
         <v>24161</v>
@@ -2644,7 +5901,46 @@
         <v>68</v>
       </c>
       <c r="G88" s="3" t="n">
-        <v>45870</v>
+        <v>45900</v>
+      </c>
+      <c r="H88" t="n">
+        <v>3</v>
+      </c>
+      <c r="I88" t="n">
+        <v>-0.8660254037844385</v>
+      </c>
+      <c r="J88" t="n">
+        <v>-0.5000000000000004</v>
+      </c>
+      <c r="K88" t="n">
+        <v>34190</v>
+      </c>
+      <c r="L88" t="n">
+        <v>30370</v>
+      </c>
+      <c r="M88" t="n">
+        <v>22739</v>
+      </c>
+      <c r="N88" t="n">
+        <v>29508.33333333333</v>
+      </c>
+      <c r="O88" t="n">
+        <v>27743.66666666667</v>
+      </c>
+      <c r="P88" t="n">
+        <v>83</v>
+      </c>
+      <c r="Q88" t="n">
+        <v>83</v>
+      </c>
+      <c r="R88" t="n">
+        <v>73.66666666666667</v>
+      </c>
+      <c r="S88" t="n">
+        <v>-15</v>
+      </c>
+      <c r="T88" t="n">
+        <v>31</v>
       </c>
     </row>
     <row r="89">
@@ -2660,7 +5956,7 @@
         <v>9</v>
       </c>
       <c r="D89" s="2" t="n">
-        <v>45901</v>
+        <v>45930</v>
       </c>
       <c r="E89" t="n">
         <v>25319</v>
@@ -2669,7 +5965,46 @@
         <v>78</v>
       </c>
       <c r="G89" s="3" t="n">
-        <v>45901</v>
+        <v>45930</v>
+      </c>
+      <c r="H89" t="n">
+        <v>3</v>
+      </c>
+      <c r="I89" t="n">
+        <v>-1</v>
+      </c>
+      <c r="J89" t="n">
+        <v>-1.83697019872103e-16</v>
+      </c>
+      <c r="K89" t="n">
+        <v>24161</v>
+      </c>
+      <c r="L89" t="n">
+        <v>23965</v>
+      </c>
+      <c r="M89" t="n">
+        <v>26385</v>
+      </c>
+      <c r="N89" t="n">
+        <v>27438.66666666667</v>
+      </c>
+      <c r="O89" t="n">
+        <v>27980.66666666667</v>
+      </c>
+      <c r="P89" t="n">
+        <v>68</v>
+      </c>
+      <c r="Q89" t="n">
+        <v>55</v>
+      </c>
+      <c r="R89" t="n">
+        <v>68.66666666666667</v>
+      </c>
+      <c r="S89" t="n">
+        <v>10</v>
+      </c>
+      <c r="T89" t="n">
+        <v>32</v>
       </c>
     </row>
     <row r="90">
@@ -2685,7 +6020,7 @@
         <v>10</v>
       </c>
       <c r="D90" s="2" t="n">
-        <v>45931</v>
+        <v>45961</v>
       </c>
       <c r="E90" t="n">
         <v>35170</v>
@@ -2694,7 +6029,46 @@
         <v>96</v>
       </c>
       <c r="G90" s="3" t="n">
-        <v>45931</v>
+        <v>45961</v>
+      </c>
+      <c r="H90" t="n">
+        <v>4</v>
+      </c>
+      <c r="I90" t="n">
+        <v>-0.8660254037844386</v>
+      </c>
+      <c r="J90" t="n">
+        <v>0.5000000000000001</v>
+      </c>
+      <c r="K90" t="n">
+        <v>25319</v>
+      </c>
+      <c r="L90" t="n">
+        <v>34190</v>
+      </c>
+      <c r="M90" t="n">
+        <v>28813</v>
+      </c>
+      <c r="N90" t="n">
+        <v>27890</v>
+      </c>
+      <c r="O90" t="n">
+        <v>27803</v>
+      </c>
+      <c r="P90" t="n">
+        <v>78</v>
+      </c>
+      <c r="Q90" t="n">
+        <v>83</v>
+      </c>
+      <c r="R90" t="n">
+        <v>76.33333333333333</v>
+      </c>
+      <c r="S90" t="n">
+        <v>18</v>
+      </c>
+      <c r="T90" t="n">
+        <v>33</v>
       </c>
     </row>
     <row r="91">
@@ -2710,7 +6084,7 @@
         <v>11</v>
       </c>
       <c r="D91" s="2" t="n">
-        <v>45962</v>
+        <v>45991</v>
       </c>
       <c r="E91" t="n">
         <v>28675</v>
@@ -2719,7 +6093,46 @@
         <v>95</v>
       </c>
       <c r="G91" s="3" t="n">
-        <v>45962</v>
+        <v>45991</v>
+      </c>
+      <c r="H91" t="n">
+        <v>4</v>
+      </c>
+      <c r="I91" t="n">
+        <v>-0.5000000000000004</v>
+      </c>
+      <c r="J91" t="n">
+        <v>0.8660254037844384</v>
+      </c>
+      <c r="K91" t="n">
+        <v>35170</v>
+      </c>
+      <c r="L91" t="n">
+        <v>24161</v>
+      </c>
+      <c r="M91" t="n">
+        <v>30370</v>
+      </c>
+      <c r="N91" t="n">
+        <v>28216.66666666667</v>
+      </c>
+      <c r="O91" t="n">
+        <v>28862.5</v>
+      </c>
+      <c r="P91" t="n">
+        <v>96</v>
+      </c>
+      <c r="Q91" t="n">
+        <v>68</v>
+      </c>
+      <c r="R91" t="n">
+        <v>80.66666666666667</v>
+      </c>
+      <c r="S91" t="n">
+        <v>-1</v>
+      </c>
+      <c r="T91" t="n">
+        <v>34</v>
       </c>
     </row>
     <row r="92">
@@ -2735,7 +6148,7 @@
         <v>12</v>
       </c>
       <c r="D92" s="2" t="n">
-        <v>45992</v>
+        <v>46022</v>
       </c>
       <c r="E92" t="n">
         <v>43006</v>
@@ -2744,7 +6157,46 @@
         <v>104</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>45992</v>
+        <v>46022</v>
+      </c>
+      <c r="H92" t="n">
+        <v>4</v>
+      </c>
+      <c r="I92" t="n">
+        <v>-2.449293598294706e-16</v>
+      </c>
+      <c r="J92" t="n">
+        <v>1</v>
+      </c>
+      <c r="K92" t="n">
+        <v>28675</v>
+      </c>
+      <c r="L92" t="n">
+        <v>25319</v>
+      </c>
+      <c r="M92" t="n">
+        <v>23965</v>
+      </c>
+      <c r="N92" t="n">
+        <v>29721.33333333333</v>
+      </c>
+      <c r="O92" t="n">
+        <v>28580</v>
+      </c>
+      <c r="P92" t="n">
+        <v>95</v>
+      </c>
+      <c r="Q92" t="n">
+        <v>78</v>
+      </c>
+      <c r="R92" t="n">
+        <v>89.66666666666667</v>
+      </c>
+      <c r="S92" t="n">
+        <v>9</v>
+      </c>
+      <c r="T92" t="n">
+        <v>35</v>
       </c>
     </row>
     <row r="93">
@@ -2760,7 +6212,7 @@
         <v>1</v>
       </c>
       <c r="D93" s="2" t="n">
-        <v>44927</v>
+        <v>44957</v>
       </c>
       <c r="E93" t="n">
         <v>43838</v>
@@ -2769,7 +6221,28 @@
         <v>245</v>
       </c>
       <c r="G93" s="3" t="n">
-        <v>44927</v>
+        <v>44957</v>
+      </c>
+      <c r="H93" t="n">
+        <v>1</v>
+      </c>
+      <c r="I93" t="n">
+        <v>0.4999999999999999</v>
+      </c>
+      <c r="J93" t="n">
+        <v>0.8660254037844387</v>
+      </c>
+      <c r="K93" t="inlineStr"/>
+      <c r="L93" t="inlineStr"/>
+      <c r="M93" t="inlineStr"/>
+      <c r="N93" t="inlineStr"/>
+      <c r="O93" t="inlineStr"/>
+      <c r="P93" t="inlineStr"/>
+      <c r="Q93" t="inlineStr"/>
+      <c r="R93" t="inlineStr"/>
+      <c r="S93" t="inlineStr"/>
+      <c r="T93" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="94">
@@ -2785,7 +6258,7 @@
         <v>2</v>
       </c>
       <c r="D94" s="2" t="n">
-        <v>44958</v>
+        <v>44985</v>
       </c>
       <c r="E94" t="n">
         <v>34041</v>
@@ -2794,7 +6267,34 @@
         <v>202</v>
       </c>
       <c r="G94" s="3" t="n">
-        <v>44958</v>
+        <v>44985</v>
+      </c>
+      <c r="H94" t="n">
+        <v>1</v>
+      </c>
+      <c r="I94" t="n">
+        <v>0.8660254037844386</v>
+      </c>
+      <c r="J94" t="n">
+        <v>0.5000000000000001</v>
+      </c>
+      <c r="K94" t="n">
+        <v>43838</v>
+      </c>
+      <c r="L94" t="inlineStr"/>
+      <c r="M94" t="inlineStr"/>
+      <c r="N94" t="inlineStr"/>
+      <c r="O94" t="inlineStr"/>
+      <c r="P94" t="n">
+        <v>245</v>
+      </c>
+      <c r="Q94" t="inlineStr"/>
+      <c r="R94" t="inlineStr"/>
+      <c r="S94" t="n">
+        <v>-43</v>
+      </c>
+      <c r="T94" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="95">
@@ -2810,7 +6310,7 @@
         <v>3</v>
       </c>
       <c r="D95" s="2" t="n">
-        <v>44986</v>
+        <v>45016</v>
       </c>
       <c r="E95" t="n">
         <v>50052</v>
@@ -2819,7 +6319,34 @@
         <v>254</v>
       </c>
       <c r="G95" s="3" t="n">
-        <v>44986</v>
+        <v>45016</v>
+      </c>
+      <c r="H95" t="n">
+        <v>1</v>
+      </c>
+      <c r="I95" t="n">
+        <v>1</v>
+      </c>
+      <c r="J95" t="n">
+        <v>6.123233995736766e-17</v>
+      </c>
+      <c r="K95" t="n">
+        <v>34041</v>
+      </c>
+      <c r="L95" t="inlineStr"/>
+      <c r="M95" t="inlineStr"/>
+      <c r="N95" t="inlineStr"/>
+      <c r="O95" t="inlineStr"/>
+      <c r="P95" t="n">
+        <v>202</v>
+      </c>
+      <c r="Q95" t="inlineStr"/>
+      <c r="R95" t="inlineStr"/>
+      <c r="S95" t="n">
+        <v>52</v>
+      </c>
+      <c r="T95" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="96">
@@ -2835,7 +6362,7 @@
         <v>4</v>
       </c>
       <c r="D96" s="2" t="n">
-        <v>45017</v>
+        <v>45046</v>
       </c>
       <c r="E96" t="n">
         <v>28210</v>
@@ -2844,7 +6371,42 @@
         <v>176</v>
       </c>
       <c r="G96" s="3" t="n">
-        <v>45017</v>
+        <v>45046</v>
+      </c>
+      <c r="H96" t="n">
+        <v>2</v>
+      </c>
+      <c r="I96" t="n">
+        <v>0.8660254037844387</v>
+      </c>
+      <c r="J96" t="n">
+        <v>-0.4999999999999998</v>
+      </c>
+      <c r="K96" t="n">
+        <v>50052</v>
+      </c>
+      <c r="L96" t="n">
+        <v>43838</v>
+      </c>
+      <c r="M96" t="inlineStr"/>
+      <c r="N96" t="n">
+        <v>42643.66666666666</v>
+      </c>
+      <c r="O96" t="inlineStr"/>
+      <c r="P96" t="n">
+        <v>254</v>
+      </c>
+      <c r="Q96" t="n">
+        <v>245</v>
+      </c>
+      <c r="R96" t="n">
+        <v>233.6666666666667</v>
+      </c>
+      <c r="S96" t="n">
+        <v>-78</v>
+      </c>
+      <c r="T96" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="97">
@@ -2860,7 +6422,7 @@
         <v>5</v>
       </c>
       <c r="D97" s="2" t="n">
-        <v>45047</v>
+        <v>45077</v>
       </c>
       <c r="E97" t="n">
         <v>40928</v>
@@ -2869,7 +6431,42 @@
         <v>215</v>
       </c>
       <c r="G97" s="3" t="n">
-        <v>45047</v>
+        <v>45077</v>
+      </c>
+      <c r="H97" t="n">
+        <v>2</v>
+      </c>
+      <c r="I97" t="n">
+        <v>0.4999999999999999</v>
+      </c>
+      <c r="J97" t="n">
+        <v>-0.8660254037844387</v>
+      </c>
+      <c r="K97" t="n">
+        <v>28210</v>
+      </c>
+      <c r="L97" t="n">
+        <v>34041</v>
+      </c>
+      <c r="M97" t="inlineStr"/>
+      <c r="N97" t="n">
+        <v>37434.33333333334</v>
+      </c>
+      <c r="O97" t="inlineStr"/>
+      <c r="P97" t="n">
+        <v>176</v>
+      </c>
+      <c r="Q97" t="n">
+        <v>202</v>
+      </c>
+      <c r="R97" t="n">
+        <v>210.6666666666667</v>
+      </c>
+      <c r="S97" t="n">
+        <v>39</v>
+      </c>
+      <c r="T97" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="98">
@@ -2885,7 +6482,7 @@
         <v>6</v>
       </c>
       <c r="D98" s="2" t="n">
-        <v>45078</v>
+        <v>45107</v>
       </c>
       <c r="E98" t="n">
         <v>27703</v>
@@ -2894,7 +6491,42 @@
         <v>139</v>
       </c>
       <c r="G98" s="3" t="n">
-        <v>45078</v>
+        <v>45107</v>
+      </c>
+      <c r="H98" t="n">
+        <v>2</v>
+      </c>
+      <c r="I98" t="n">
+        <v>1.224646799147353e-16</v>
+      </c>
+      <c r="J98" t="n">
+        <v>-1</v>
+      </c>
+      <c r="K98" t="n">
+        <v>40928</v>
+      </c>
+      <c r="L98" t="n">
+        <v>50052</v>
+      </c>
+      <c r="M98" t="inlineStr"/>
+      <c r="N98" t="n">
+        <v>39730</v>
+      </c>
+      <c r="O98" t="inlineStr"/>
+      <c r="P98" t="n">
+        <v>215</v>
+      </c>
+      <c r="Q98" t="n">
+        <v>254</v>
+      </c>
+      <c r="R98" t="n">
+        <v>215</v>
+      </c>
+      <c r="S98" t="n">
+        <v>-76</v>
+      </c>
+      <c r="T98" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="99">
@@ -2910,7 +6542,7 @@
         <v>7</v>
       </c>
       <c r="D99" s="2" t="n">
-        <v>45108</v>
+        <v>45138</v>
       </c>
       <c r="E99" t="n">
         <v>24213</v>
@@ -2919,7 +6551,46 @@
         <v>111</v>
       </c>
       <c r="G99" s="3" t="n">
-        <v>45108</v>
+        <v>45138</v>
+      </c>
+      <c r="H99" t="n">
+        <v>3</v>
+      </c>
+      <c r="I99" t="n">
+        <v>-0.4999999999999997</v>
+      </c>
+      <c r="J99" t="n">
+        <v>-0.8660254037844388</v>
+      </c>
+      <c r="K99" t="n">
+        <v>27703</v>
+      </c>
+      <c r="L99" t="n">
+        <v>28210</v>
+      </c>
+      <c r="M99" t="n">
+        <v>43838</v>
+      </c>
+      <c r="N99" t="n">
+        <v>32280.33333333333</v>
+      </c>
+      <c r="O99" t="n">
+        <v>37462</v>
+      </c>
+      <c r="P99" t="n">
+        <v>139</v>
+      </c>
+      <c r="Q99" t="n">
+        <v>176</v>
+      </c>
+      <c r="R99" t="n">
+        <v>176.6666666666667</v>
+      </c>
+      <c r="S99" t="n">
+        <v>-28</v>
+      </c>
+      <c r="T99" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="100">
@@ -2935,7 +6606,7 @@
         <v>8</v>
       </c>
       <c r="D100" s="2" t="n">
-        <v>45139</v>
+        <v>45169</v>
       </c>
       <c r="E100" t="n">
         <v>82046</v>
@@ -2944,7 +6615,46 @@
         <v>295</v>
       </c>
       <c r="G100" s="3" t="n">
-        <v>45139</v>
+        <v>45169</v>
+      </c>
+      <c r="H100" t="n">
+        <v>3</v>
+      </c>
+      <c r="I100" t="n">
+        <v>-0.8660254037844385</v>
+      </c>
+      <c r="J100" t="n">
+        <v>-0.5000000000000004</v>
+      </c>
+      <c r="K100" t="n">
+        <v>24213</v>
+      </c>
+      <c r="L100" t="n">
+        <v>40928</v>
+      </c>
+      <c r="M100" t="n">
+        <v>34041</v>
+      </c>
+      <c r="N100" t="n">
+        <v>30948</v>
+      </c>
+      <c r="O100" t="n">
+        <v>34191.16666666666</v>
+      </c>
+      <c r="P100" t="n">
+        <v>111</v>
+      </c>
+      <c r="Q100" t="n">
+        <v>215</v>
+      </c>
+      <c r="R100" t="n">
+        <v>155</v>
+      </c>
+      <c r="S100" t="n">
+        <v>184</v>
+      </c>
+      <c r="T100" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="101">
@@ -2960,7 +6670,7 @@
         <v>9</v>
       </c>
       <c r="D101" s="2" t="n">
-        <v>45170</v>
+        <v>45199</v>
       </c>
       <c r="E101" t="n">
         <v>32787</v>
@@ -2969,7 +6679,46 @@
         <v>162</v>
       </c>
       <c r="G101" s="3" t="n">
-        <v>45170</v>
+        <v>45199</v>
+      </c>
+      <c r="H101" t="n">
+        <v>3</v>
+      </c>
+      <c r="I101" t="n">
+        <v>-1</v>
+      </c>
+      <c r="J101" t="n">
+        <v>-1.83697019872103e-16</v>
+      </c>
+      <c r="K101" t="n">
+        <v>82046</v>
+      </c>
+      <c r="L101" t="n">
+        <v>27703</v>
+      </c>
+      <c r="M101" t="n">
+        <v>50052</v>
+      </c>
+      <c r="N101" t="n">
+        <v>44654</v>
+      </c>
+      <c r="O101" t="n">
+        <v>42192</v>
+      </c>
+      <c r="P101" t="n">
+        <v>295</v>
+      </c>
+      <c r="Q101" t="n">
+        <v>139</v>
+      </c>
+      <c r="R101" t="n">
+        <v>181.6666666666667</v>
+      </c>
+      <c r="S101" t="n">
+        <v>-133</v>
+      </c>
+      <c r="T101" t="n">
+        <v>8</v>
       </c>
     </row>
     <row r="102">
@@ -2985,7 +6734,7 @@
         <v>10</v>
       </c>
       <c r="D102" s="2" t="n">
-        <v>45200</v>
+        <v>45230</v>
       </c>
       <c r="E102" t="n">
         <v>46347</v>
@@ -2994,7 +6743,46 @@
         <v>259</v>
       </c>
       <c r="G102" s="3" t="n">
-        <v>45200</v>
+        <v>45230</v>
+      </c>
+      <c r="H102" t="n">
+        <v>4</v>
+      </c>
+      <c r="I102" t="n">
+        <v>-0.8660254037844386</v>
+      </c>
+      <c r="J102" t="n">
+        <v>0.5000000000000001</v>
+      </c>
+      <c r="K102" t="n">
+        <v>32787</v>
+      </c>
+      <c r="L102" t="n">
+        <v>24213</v>
+      </c>
+      <c r="M102" t="n">
+        <v>28210</v>
+      </c>
+      <c r="N102" t="n">
+        <v>46348.66666666666</v>
+      </c>
+      <c r="O102" t="n">
+        <v>39314.5</v>
+      </c>
+      <c r="P102" t="n">
+        <v>162</v>
+      </c>
+      <c r="Q102" t="n">
+        <v>111</v>
+      </c>
+      <c r="R102" t="n">
+        <v>189.3333333333333</v>
+      </c>
+      <c r="S102" t="n">
+        <v>97</v>
+      </c>
+      <c r="T102" t="n">
+        <v>9</v>
       </c>
     </row>
     <row r="103">
@@ -3010,7 +6798,7 @@
         <v>11</v>
       </c>
       <c r="D103" s="2" t="n">
-        <v>45231</v>
+        <v>45260</v>
       </c>
       <c r="E103" t="n">
         <v>36492</v>
@@ -3019,7 +6807,46 @@
         <v>240</v>
       </c>
       <c r="G103" s="3" t="n">
-        <v>45231</v>
+        <v>45260</v>
+      </c>
+      <c r="H103" t="n">
+        <v>4</v>
+      </c>
+      <c r="I103" t="n">
+        <v>-0.5000000000000004</v>
+      </c>
+      <c r="J103" t="n">
+        <v>0.8660254037844384</v>
+      </c>
+      <c r="K103" t="n">
+        <v>46347</v>
+      </c>
+      <c r="L103" t="n">
+        <v>82046</v>
+      </c>
+      <c r="M103" t="n">
+        <v>40928</v>
+      </c>
+      <c r="N103" t="n">
+        <v>53726.66666666666</v>
+      </c>
+      <c r="O103" t="n">
+        <v>42337.33333333334</v>
+      </c>
+      <c r="P103" t="n">
+        <v>259</v>
+      </c>
+      <c r="Q103" t="n">
+        <v>295</v>
+      </c>
+      <c r="R103" t="n">
+        <v>238.6666666666667</v>
+      </c>
+      <c r="S103" t="n">
+        <v>-19</v>
+      </c>
+      <c r="T103" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="104">
@@ -3035,7 +6862,7 @@
         <v>12</v>
       </c>
       <c r="D104" s="2" t="n">
-        <v>45261</v>
+        <v>45291</v>
       </c>
       <c r="E104" t="n">
         <v>28997</v>
@@ -3044,7 +6871,46 @@
         <v>177</v>
       </c>
       <c r="G104" s="3" t="n">
-        <v>45261</v>
+        <v>45291</v>
+      </c>
+      <c r="H104" t="n">
+        <v>4</v>
+      </c>
+      <c r="I104" t="n">
+        <v>-2.449293598294706e-16</v>
+      </c>
+      <c r="J104" t="n">
+        <v>1</v>
+      </c>
+      <c r="K104" t="n">
+        <v>36492</v>
+      </c>
+      <c r="L104" t="n">
+        <v>32787</v>
+      </c>
+      <c r="M104" t="n">
+        <v>27703</v>
+      </c>
+      <c r="N104" t="n">
+        <v>38542</v>
+      </c>
+      <c r="O104" t="n">
+        <v>41598</v>
+      </c>
+      <c r="P104" t="n">
+        <v>240</v>
+      </c>
+      <c r="Q104" t="n">
+        <v>162</v>
+      </c>
+      <c r="R104" t="n">
+        <v>220.3333333333333</v>
+      </c>
+      <c r="S104" t="n">
+        <v>-63</v>
+      </c>
+      <c r="T104" t="n">
+        <v>11</v>
       </c>
     </row>
     <row r="105">
@@ -3060,7 +6926,7 @@
         <v>1</v>
       </c>
       <c r="D105" s="2" t="n">
-        <v>45292</v>
+        <v>45322</v>
       </c>
       <c r="E105" t="n">
         <v>33612</v>
@@ -3069,7 +6935,46 @@
         <v>228</v>
       </c>
       <c r="G105" s="3" t="n">
-        <v>45292</v>
+        <v>45322</v>
+      </c>
+      <c r="H105" t="n">
+        <v>1</v>
+      </c>
+      <c r="I105" t="n">
+        <v>0.4999999999999999</v>
+      </c>
+      <c r="J105" t="n">
+        <v>0.8660254037844387</v>
+      </c>
+      <c r="K105" t="n">
+        <v>28997</v>
+      </c>
+      <c r="L105" t="n">
+        <v>46347</v>
+      </c>
+      <c r="M105" t="n">
+        <v>24213</v>
+      </c>
+      <c r="N105" t="n">
+        <v>37278.66666666666</v>
+      </c>
+      <c r="O105" t="n">
+        <v>41813.66666666666</v>
+      </c>
+      <c r="P105" t="n">
+        <v>177</v>
+      </c>
+      <c r="Q105" t="n">
+        <v>259</v>
+      </c>
+      <c r="R105" t="n">
+        <v>225.3333333333333</v>
+      </c>
+      <c r="S105" t="n">
+        <v>51</v>
+      </c>
+      <c r="T105" t="n">
+        <v>12</v>
       </c>
     </row>
     <row r="106">
@@ -3085,7 +6990,7 @@
         <v>2</v>
       </c>
       <c r="D106" s="2" t="n">
-        <v>45323</v>
+        <v>45351</v>
       </c>
       <c r="E106" t="n">
         <v>32642</v>
@@ -3094,7 +6999,46 @@
         <v>220</v>
       </c>
       <c r="G106" s="3" t="n">
-        <v>45323</v>
+        <v>45351</v>
+      </c>
+      <c r="H106" t="n">
+        <v>1</v>
+      </c>
+      <c r="I106" t="n">
+        <v>0.8660254037844386</v>
+      </c>
+      <c r="J106" t="n">
+        <v>0.5000000000000001</v>
+      </c>
+      <c r="K106" t="n">
+        <v>33612</v>
+      </c>
+      <c r="L106" t="n">
+        <v>36492</v>
+      </c>
+      <c r="M106" t="n">
+        <v>82046</v>
+      </c>
+      <c r="N106" t="n">
+        <v>33033.66666666666</v>
+      </c>
+      <c r="O106" t="n">
+        <v>43380.16666666666</v>
+      </c>
+      <c r="P106" t="n">
+        <v>228</v>
+      </c>
+      <c r="Q106" t="n">
+        <v>240</v>
+      </c>
+      <c r="R106" t="n">
+        <v>215</v>
+      </c>
+      <c r="S106" t="n">
+        <v>-8</v>
+      </c>
+      <c r="T106" t="n">
+        <v>13</v>
       </c>
     </row>
     <row r="107">
@@ -3110,7 +7054,7 @@
         <v>3</v>
       </c>
       <c r="D107" s="2" t="n">
-        <v>45352</v>
+        <v>45382</v>
       </c>
       <c r="E107" t="n">
         <v>33685</v>
@@ -3119,7 +7063,46 @@
         <v>195</v>
       </c>
       <c r="G107" s="3" t="n">
-        <v>45352</v>
+        <v>45382</v>
+      </c>
+      <c r="H107" t="n">
+        <v>1</v>
+      </c>
+      <c r="I107" t="n">
+        <v>1</v>
+      </c>
+      <c r="J107" t="n">
+        <v>6.123233995736766e-17</v>
+      </c>
+      <c r="K107" t="n">
+        <v>32642</v>
+      </c>
+      <c r="L107" t="n">
+        <v>28997</v>
+      </c>
+      <c r="M107" t="n">
+        <v>32787</v>
+      </c>
+      <c r="N107" t="n">
+        <v>31750.33333333333</v>
+      </c>
+      <c r="O107" t="n">
+        <v>35146.16666666666</v>
+      </c>
+      <c r="P107" t="n">
+        <v>220</v>
+      </c>
+      <c r="Q107" t="n">
+        <v>177</v>
+      </c>
+      <c r="R107" t="n">
+        <v>208.3333333333333</v>
+      </c>
+      <c r="S107" t="n">
+        <v>-25</v>
+      </c>
+      <c r="T107" t="n">
+        <v>14</v>
       </c>
     </row>
     <row r="108">
@@ -3135,7 +7118,7 @@
         <v>4</v>
       </c>
       <c r="D108" s="2" t="n">
-        <v>45383</v>
+        <v>45412</v>
       </c>
       <c r="E108" t="n">
         <v>65578</v>
@@ -3144,7 +7127,46 @@
         <v>246</v>
       </c>
       <c r="G108" s="3" t="n">
-        <v>45383</v>
+        <v>45412</v>
+      </c>
+      <c r="H108" t="n">
+        <v>2</v>
+      </c>
+      <c r="I108" t="n">
+        <v>0.8660254037844387</v>
+      </c>
+      <c r="J108" t="n">
+        <v>-0.4999999999999998</v>
+      </c>
+      <c r="K108" t="n">
+        <v>33685</v>
+      </c>
+      <c r="L108" t="n">
+        <v>33612</v>
+      </c>
+      <c r="M108" t="n">
+        <v>46347</v>
+      </c>
+      <c r="N108" t="n">
+        <v>33313</v>
+      </c>
+      <c r="O108" t="n">
+        <v>35295.83333333334</v>
+      </c>
+      <c r="P108" t="n">
+        <v>195</v>
+      </c>
+      <c r="Q108" t="n">
+        <v>228</v>
+      </c>
+      <c r="R108" t="n">
+        <v>214.3333333333333</v>
+      </c>
+      <c r="S108" t="n">
+        <v>51</v>
+      </c>
+      <c r="T108" t="n">
+        <v>15</v>
       </c>
     </row>
     <row r="109">
@@ -3160,7 +7182,7 @@
         <v>5</v>
       </c>
       <c r="D109" s="2" t="n">
-        <v>45413</v>
+        <v>45443</v>
       </c>
       <c r="E109" t="n">
         <v>51442</v>
@@ -3169,7 +7191,46 @@
         <v>257</v>
       </c>
       <c r="G109" s="3" t="n">
-        <v>45413</v>
+        <v>45443</v>
+      </c>
+      <c r="H109" t="n">
+        <v>2</v>
+      </c>
+      <c r="I109" t="n">
+        <v>0.4999999999999999</v>
+      </c>
+      <c r="J109" t="n">
+        <v>-0.8660254037844387</v>
+      </c>
+      <c r="K109" t="n">
+        <v>65578</v>
+      </c>
+      <c r="L109" t="n">
+        <v>32642</v>
+      </c>
+      <c r="M109" t="n">
+        <v>36492</v>
+      </c>
+      <c r="N109" t="n">
+        <v>43968.33333333334</v>
+      </c>
+      <c r="O109" t="n">
+        <v>38501</v>
+      </c>
+      <c r="P109" t="n">
+        <v>246</v>
+      </c>
+      <c r="Q109" t="n">
+        <v>220</v>
+      </c>
+      <c r="R109" t="n">
+        <v>220.3333333333333</v>
+      </c>
+      <c r="S109" t="n">
+        <v>11</v>
+      </c>
+      <c r="T109" t="n">
+        <v>16</v>
       </c>
     </row>
     <row r="110">
@@ -3185,7 +7246,7 @@
         <v>6</v>
       </c>
       <c r="D110" s="2" t="n">
-        <v>45444</v>
+        <v>45473</v>
       </c>
       <c r="E110" t="n">
         <v>44786</v>
@@ -3194,7 +7255,46 @@
         <v>171</v>
       </c>
       <c r="G110" s="3" t="n">
-        <v>45444</v>
+        <v>45473</v>
+      </c>
+      <c r="H110" t="n">
+        <v>2</v>
+      </c>
+      <c r="I110" t="n">
+        <v>1.224646799147353e-16</v>
+      </c>
+      <c r="J110" t="n">
+        <v>-1</v>
+      </c>
+      <c r="K110" t="n">
+        <v>51442</v>
+      </c>
+      <c r="L110" t="n">
+        <v>33685</v>
+      </c>
+      <c r="M110" t="n">
+        <v>28997</v>
+      </c>
+      <c r="N110" t="n">
+        <v>50235</v>
+      </c>
+      <c r="O110" t="n">
+        <v>40992.66666666666</v>
+      </c>
+      <c r="P110" t="n">
+        <v>257</v>
+      </c>
+      <c r="Q110" t="n">
+        <v>195</v>
+      </c>
+      <c r="R110" t="n">
+        <v>232.6666666666667</v>
+      </c>
+      <c r="S110" t="n">
+        <v>-86</v>
+      </c>
+      <c r="T110" t="n">
+        <v>17</v>
       </c>
     </row>
     <row r="111">
@@ -3210,7 +7310,7 @@
         <v>7</v>
       </c>
       <c r="D111" s="2" t="n">
-        <v>45474</v>
+        <v>45504</v>
       </c>
       <c r="E111" t="n">
         <v>41281</v>
@@ -3219,7 +7319,46 @@
         <v>181</v>
       </c>
       <c r="G111" s="3" t="n">
-        <v>45474</v>
+        <v>45504</v>
+      </c>
+      <c r="H111" t="n">
+        <v>3</v>
+      </c>
+      <c r="I111" t="n">
+        <v>-0.4999999999999997</v>
+      </c>
+      <c r="J111" t="n">
+        <v>-0.8660254037844388</v>
+      </c>
+      <c r="K111" t="n">
+        <v>44786</v>
+      </c>
+      <c r="L111" t="n">
+        <v>65578</v>
+      </c>
+      <c r="M111" t="n">
+        <v>33612</v>
+      </c>
+      <c r="N111" t="n">
+        <v>53935.33333333334</v>
+      </c>
+      <c r="O111" t="n">
+        <v>43624.16666666666</v>
+      </c>
+      <c r="P111" t="n">
+        <v>171</v>
+      </c>
+      <c r="Q111" t="n">
+        <v>246</v>
+      </c>
+      <c r="R111" t="n">
+        <v>224.6666666666667</v>
+      </c>
+      <c r="S111" t="n">
+        <v>10</v>
+      </c>
+      <c r="T111" t="n">
+        <v>18</v>
       </c>
     </row>
     <row r="112">
@@ -3235,7 +7374,7 @@
         <v>8</v>
       </c>
       <c r="D112" s="2" t="n">
-        <v>45505</v>
+        <v>45535</v>
       </c>
       <c r="E112" t="n">
         <v>49214</v>
@@ -3244,7 +7383,46 @@
         <v>264</v>
       </c>
       <c r="G112" s="3" t="n">
-        <v>45505</v>
+        <v>45535</v>
+      </c>
+      <c r="H112" t="n">
+        <v>3</v>
+      </c>
+      <c r="I112" t="n">
+        <v>-0.8660254037844385</v>
+      </c>
+      <c r="J112" t="n">
+        <v>-0.5000000000000004</v>
+      </c>
+      <c r="K112" t="n">
+        <v>41281</v>
+      </c>
+      <c r="L112" t="n">
+        <v>51442</v>
+      </c>
+      <c r="M112" t="n">
+        <v>32642</v>
+      </c>
+      <c r="N112" t="n">
+        <v>45836.33333333334</v>
+      </c>
+      <c r="O112" t="n">
+        <v>44902.33333333334</v>
+      </c>
+      <c r="P112" t="n">
+        <v>181</v>
+      </c>
+      <c r="Q112" t="n">
+        <v>257</v>
+      </c>
+      <c r="R112" t="n">
+        <v>203</v>
+      </c>
+      <c r="S112" t="n">
+        <v>83</v>
+      </c>
+      <c r="T112" t="n">
+        <v>19</v>
       </c>
     </row>
     <row r="113">
@@ -3260,7 +7438,7 @@
         <v>9</v>
       </c>
       <c r="D113" s="2" t="n">
-        <v>45536</v>
+        <v>45565</v>
       </c>
       <c r="E113" t="n">
         <v>43606</v>
@@ -3269,7 +7447,46 @@
         <v>235</v>
       </c>
       <c r="G113" s="3" t="n">
-        <v>45536</v>
+        <v>45565</v>
+      </c>
+      <c r="H113" t="n">
+        <v>3</v>
+      </c>
+      <c r="I113" t="n">
+        <v>-1</v>
+      </c>
+      <c r="J113" t="n">
+        <v>-1.83697019872103e-16</v>
+      </c>
+      <c r="K113" t="n">
+        <v>49214</v>
+      </c>
+      <c r="L113" t="n">
+        <v>44786</v>
+      </c>
+      <c r="M113" t="n">
+        <v>33685</v>
+      </c>
+      <c r="N113" t="n">
+        <v>45093.66666666666</v>
+      </c>
+      <c r="O113" t="n">
+        <v>47664.33333333334</v>
+      </c>
+      <c r="P113" t="n">
+        <v>264</v>
+      </c>
+      <c r="Q113" t="n">
+        <v>171</v>
+      </c>
+      <c r="R113" t="n">
+        <v>205.3333333333333</v>
+      </c>
+      <c r="S113" t="n">
+        <v>-29</v>
+      </c>
+      <c r="T113" t="n">
+        <v>20</v>
       </c>
     </row>
     <row r="114">
@@ -3285,7 +7502,7 @@
         <v>10</v>
       </c>
       <c r="D114" s="2" t="n">
-        <v>45566</v>
+        <v>45596</v>
       </c>
       <c r="E114" t="n">
         <v>51653</v>
@@ -3294,7 +7511,46 @@
         <v>294</v>
       </c>
       <c r="G114" s="3" t="n">
-        <v>45566</v>
+        <v>45596</v>
+      </c>
+      <c r="H114" t="n">
+        <v>4</v>
+      </c>
+      <c r="I114" t="n">
+        <v>-0.8660254037844386</v>
+      </c>
+      <c r="J114" t="n">
+        <v>0.5000000000000001</v>
+      </c>
+      <c r="K114" t="n">
+        <v>43606</v>
+      </c>
+      <c r="L114" t="n">
+        <v>41281</v>
+      </c>
+      <c r="M114" t="n">
+        <v>65578</v>
+      </c>
+      <c r="N114" t="n">
+        <v>44700.33333333334</v>
+      </c>
+      <c r="O114" t="n">
+        <v>49317.83333333334</v>
+      </c>
+      <c r="P114" t="n">
+        <v>235</v>
+      </c>
+      <c r="Q114" t="n">
+        <v>181</v>
+      </c>
+      <c r="R114" t="n">
+        <v>226.6666666666667</v>
+      </c>
+      <c r="S114" t="n">
+        <v>59</v>
+      </c>
+      <c r="T114" t="n">
+        <v>21</v>
       </c>
     </row>
     <row r="115">
@@ -3310,7 +7566,7 @@
         <v>11</v>
       </c>
       <c r="D115" s="2" t="n">
-        <v>45597</v>
+        <v>45626</v>
       </c>
       <c r="E115" t="n">
         <v>52108</v>
@@ -3319,7 +7575,46 @@
         <v>268</v>
       </c>
       <c r="G115" s="3" t="n">
-        <v>45597</v>
+        <v>45626</v>
+      </c>
+      <c r="H115" t="n">
+        <v>4</v>
+      </c>
+      <c r="I115" t="n">
+        <v>-0.5000000000000004</v>
+      </c>
+      <c r="J115" t="n">
+        <v>0.8660254037844384</v>
+      </c>
+      <c r="K115" t="n">
+        <v>51653</v>
+      </c>
+      <c r="L115" t="n">
+        <v>49214</v>
+      </c>
+      <c r="M115" t="n">
+        <v>51442</v>
+      </c>
+      <c r="N115" t="n">
+        <v>48157.66666666666</v>
+      </c>
+      <c r="O115" t="n">
+        <v>46997</v>
+      </c>
+      <c r="P115" t="n">
+        <v>294</v>
+      </c>
+      <c r="Q115" t="n">
+        <v>264</v>
+      </c>
+      <c r="R115" t="n">
+        <v>264.3333333333333</v>
+      </c>
+      <c r="S115" t="n">
+        <v>-26</v>
+      </c>
+      <c r="T115" t="n">
+        <v>22</v>
       </c>
     </row>
     <row r="116">
@@ -3335,7 +7630,7 @@
         <v>12</v>
       </c>
       <c r="D116" s="2" t="n">
-        <v>45627</v>
+        <v>45657</v>
       </c>
       <c r="E116" t="n">
         <v>37027</v>
@@ -3344,7 +7639,46 @@
         <v>219</v>
       </c>
       <c r="G116" s="3" t="n">
-        <v>45627</v>
+        <v>45657</v>
+      </c>
+      <c r="H116" t="n">
+        <v>4</v>
+      </c>
+      <c r="I116" t="n">
+        <v>-2.449293598294706e-16</v>
+      </c>
+      <c r="J116" t="n">
+        <v>1</v>
+      </c>
+      <c r="K116" t="n">
+        <v>52108</v>
+      </c>
+      <c r="L116" t="n">
+        <v>43606</v>
+      </c>
+      <c r="M116" t="n">
+        <v>44786</v>
+      </c>
+      <c r="N116" t="n">
+        <v>49122.33333333334</v>
+      </c>
+      <c r="O116" t="n">
+        <v>47108</v>
+      </c>
+      <c r="P116" t="n">
+        <v>268</v>
+      </c>
+      <c r="Q116" t="n">
+        <v>235</v>
+      </c>
+      <c r="R116" t="n">
+        <v>265.6666666666667</v>
+      </c>
+      <c r="S116" t="n">
+        <v>-49</v>
+      </c>
+      <c r="T116" t="n">
+        <v>23</v>
       </c>
     </row>
     <row r="117">
@@ -3360,7 +7694,7 @@
         <v>1</v>
       </c>
       <c r="D117" s="2" t="n">
-        <v>45658</v>
+        <v>45688</v>
       </c>
       <c r="E117" t="n">
         <v>48674</v>
@@ -3369,7 +7703,46 @@
         <v>260</v>
       </c>
       <c r="G117" s="3" t="n">
-        <v>45658</v>
+        <v>45688</v>
+      </c>
+      <c r="H117" t="n">
+        <v>1</v>
+      </c>
+      <c r="I117" t="n">
+        <v>0.4999999999999999</v>
+      </c>
+      <c r="J117" t="n">
+        <v>0.8660254037844387</v>
+      </c>
+      <c r="K117" t="n">
+        <v>37027</v>
+      </c>
+      <c r="L117" t="n">
+        <v>51653</v>
+      </c>
+      <c r="M117" t="n">
+        <v>41281</v>
+      </c>
+      <c r="N117" t="n">
+        <v>46929.33333333334</v>
+      </c>
+      <c r="O117" t="n">
+        <v>45814.83333333334</v>
+      </c>
+      <c r="P117" t="n">
+        <v>219</v>
+      </c>
+      <c r="Q117" t="n">
+        <v>294</v>
+      </c>
+      <c r="R117" t="n">
+        <v>260.3333333333333</v>
+      </c>
+      <c r="S117" t="n">
+        <v>41</v>
+      </c>
+      <c r="T117" t="n">
+        <v>24</v>
       </c>
     </row>
     <row r="118">
@@ -3385,7 +7758,7 @@
         <v>2</v>
       </c>
       <c r="D118" s="2" t="n">
-        <v>45689</v>
+        <v>45716</v>
       </c>
       <c r="E118" t="n">
         <v>38753</v>
@@ -3394,7 +7767,46 @@
         <v>225</v>
       </c>
       <c r="G118" s="3" t="n">
-        <v>45689</v>
+        <v>45716</v>
+      </c>
+      <c r="H118" t="n">
+        <v>1</v>
+      </c>
+      <c r="I118" t="n">
+        <v>0.8660254037844386</v>
+      </c>
+      <c r="J118" t="n">
+        <v>0.5000000000000001</v>
+      </c>
+      <c r="K118" t="n">
+        <v>48674</v>
+      </c>
+      <c r="L118" t="n">
+        <v>52108</v>
+      </c>
+      <c r="M118" t="n">
+        <v>49214</v>
+      </c>
+      <c r="N118" t="n">
+        <v>45936.33333333334</v>
+      </c>
+      <c r="O118" t="n">
+        <v>47047</v>
+      </c>
+      <c r="P118" t="n">
+        <v>260</v>
+      </c>
+      <c r="Q118" t="n">
+        <v>268</v>
+      </c>
+      <c r="R118" t="n">
+        <v>249</v>
+      </c>
+      <c r="S118" t="n">
+        <v>-35</v>
+      </c>
+      <c r="T118" t="n">
+        <v>25</v>
       </c>
     </row>
     <row r="119">
@@ -3410,7 +7822,7 @@
         <v>3</v>
       </c>
       <c r="D119" s="2" t="n">
-        <v>45717</v>
+        <v>45747</v>
       </c>
       <c r="E119" t="n">
         <v>31455</v>
@@ -3419,7 +7831,46 @@
         <v>202</v>
       </c>
       <c r="G119" s="3" t="n">
-        <v>45717</v>
+        <v>45747</v>
+      </c>
+      <c r="H119" t="n">
+        <v>1</v>
+      </c>
+      <c r="I119" t="n">
+        <v>1</v>
+      </c>
+      <c r="J119" t="n">
+        <v>6.123233995736766e-17</v>
+      </c>
+      <c r="K119" t="n">
+        <v>38753</v>
+      </c>
+      <c r="L119" t="n">
+        <v>37027</v>
+      </c>
+      <c r="M119" t="n">
+        <v>43606</v>
+      </c>
+      <c r="N119" t="n">
+        <v>41484.66666666666</v>
+      </c>
+      <c r="O119" t="n">
+        <v>45303.5</v>
+      </c>
+      <c r="P119" t="n">
+        <v>225</v>
+      </c>
+      <c r="Q119" t="n">
+        <v>219</v>
+      </c>
+      <c r="R119" t="n">
+        <v>234.6666666666667</v>
+      </c>
+      <c r="S119" t="n">
+        <v>-23</v>
+      </c>
+      <c r="T119" t="n">
+        <v>26</v>
       </c>
     </row>
     <row r="120">
@@ -3435,7 +7886,7 @@
         <v>4</v>
       </c>
       <c r="D120" s="2" t="n">
-        <v>45748</v>
+        <v>45777</v>
       </c>
       <c r="E120" t="n">
         <v>35596</v>
@@ -3444,7 +7895,46 @@
         <v>257</v>
       </c>
       <c r="G120" s="3" t="n">
-        <v>45748</v>
+        <v>45777</v>
+      </c>
+      <c r="H120" t="n">
+        <v>2</v>
+      </c>
+      <c r="I120" t="n">
+        <v>0.8660254037844387</v>
+      </c>
+      <c r="J120" t="n">
+        <v>-0.4999999999999998</v>
+      </c>
+      <c r="K120" t="n">
+        <v>31455</v>
+      </c>
+      <c r="L120" t="n">
+        <v>48674</v>
+      </c>
+      <c r="M120" t="n">
+        <v>51653</v>
+      </c>
+      <c r="N120" t="n">
+        <v>39627.33333333334</v>
+      </c>
+      <c r="O120" t="n">
+        <v>43278.33333333334</v>
+      </c>
+      <c r="P120" t="n">
+        <v>202</v>
+      </c>
+      <c r="Q120" t="n">
+        <v>260</v>
+      </c>
+      <c r="R120" t="n">
+        <v>229</v>
+      </c>
+      <c r="S120" t="n">
+        <v>55</v>
+      </c>
+      <c r="T120" t="n">
+        <v>27</v>
       </c>
     </row>
     <row r="121">
@@ -3460,7 +7950,7 @@
         <v>5</v>
       </c>
       <c r="D121" s="2" t="n">
-        <v>45778</v>
+        <v>45808</v>
       </c>
       <c r="E121" t="n">
         <v>22850</v>
@@ -3469,7 +7959,46 @@
         <v>177</v>
       </c>
       <c r="G121" s="3" t="n">
-        <v>45778</v>
+        <v>45808</v>
+      </c>
+      <c r="H121" t="n">
+        <v>2</v>
+      </c>
+      <c r="I121" t="n">
+        <v>0.4999999999999999</v>
+      </c>
+      <c r="J121" t="n">
+        <v>-0.8660254037844387</v>
+      </c>
+      <c r="K121" t="n">
+        <v>35596</v>
+      </c>
+      <c r="L121" t="n">
+        <v>38753</v>
+      </c>
+      <c r="M121" t="n">
+        <v>52108</v>
+      </c>
+      <c r="N121" t="n">
+        <v>35268</v>
+      </c>
+      <c r="O121" t="n">
+        <v>40602.16666666666</v>
+      </c>
+      <c r="P121" t="n">
+        <v>257</v>
+      </c>
+      <c r="Q121" t="n">
+        <v>225</v>
+      </c>
+      <c r="R121" t="n">
+        <v>228</v>
+      </c>
+      <c r="S121" t="n">
+        <v>-80</v>
+      </c>
+      <c r="T121" t="n">
+        <v>28</v>
       </c>
     </row>
     <row r="122">
@@ -3485,7 +8014,7 @@
         <v>6</v>
       </c>
       <c r="D122" s="2" t="n">
-        <v>45809</v>
+        <v>45838</v>
       </c>
       <c r="E122" t="n">
         <v>21700</v>
@@ -3494,7 +8023,46 @@
         <v>134</v>
       </c>
       <c r="G122" s="3" t="n">
-        <v>45809</v>
+        <v>45838</v>
+      </c>
+      <c r="H122" t="n">
+        <v>2</v>
+      </c>
+      <c r="I122" t="n">
+        <v>1.224646799147353e-16</v>
+      </c>
+      <c r="J122" t="n">
+        <v>-1</v>
+      </c>
+      <c r="K122" t="n">
+        <v>22850</v>
+      </c>
+      <c r="L122" t="n">
+        <v>31455</v>
+      </c>
+      <c r="M122" t="n">
+        <v>37027</v>
+      </c>
+      <c r="N122" t="n">
+        <v>29967</v>
+      </c>
+      <c r="O122" t="n">
+        <v>35725.83333333334</v>
+      </c>
+      <c r="P122" t="n">
+        <v>177</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>202</v>
+      </c>
+      <c r="R122" t="n">
+        <v>212</v>
+      </c>
+      <c r="S122" t="n">
+        <v>-43</v>
+      </c>
+      <c r="T122" t="n">
+        <v>29</v>
       </c>
     </row>
     <row r="123">
@@ -3510,7 +8078,7 @@
         <v>7</v>
       </c>
       <c r="D123" s="2" t="n">
-        <v>45839</v>
+        <v>45869</v>
       </c>
       <c r="E123" t="n">
         <v>25000</v>
@@ -3519,7 +8087,46 @@
         <v>159</v>
       </c>
       <c r="G123" s="3" t="n">
-        <v>45839</v>
+        <v>45869</v>
+      </c>
+      <c r="H123" t="n">
+        <v>3</v>
+      </c>
+      <c r="I123" t="n">
+        <v>-0.4999999999999997</v>
+      </c>
+      <c r="J123" t="n">
+        <v>-0.8660254037844388</v>
+      </c>
+      <c r="K123" t="n">
+        <v>21700</v>
+      </c>
+      <c r="L123" t="n">
+        <v>35596</v>
+      </c>
+      <c r="M123" t="n">
+        <v>48674</v>
+      </c>
+      <c r="N123" t="n">
+        <v>26715.33333333333</v>
+      </c>
+      <c r="O123" t="n">
+        <v>33171.33333333334</v>
+      </c>
+      <c r="P123" t="n">
+        <v>134</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>257</v>
+      </c>
+      <c r="R123" t="n">
+        <v>189.3333333333333</v>
+      </c>
+      <c r="S123" t="n">
+        <v>25</v>
+      </c>
+      <c r="T123" t="n">
+        <v>30</v>
       </c>
     </row>
     <row r="124">
@@ -3535,7 +8142,7 @@
         <v>8</v>
       </c>
       <c r="D124" s="2" t="n">
-        <v>45870</v>
+        <v>45900</v>
       </c>
       <c r="E124" t="n">
         <v>22156</v>
@@ -3544,7 +8151,46 @@
         <v>143</v>
       </c>
       <c r="G124" s="3" t="n">
-        <v>45870</v>
+        <v>45900</v>
+      </c>
+      <c r="H124" t="n">
+        <v>3</v>
+      </c>
+      <c r="I124" t="n">
+        <v>-0.8660254037844385</v>
+      </c>
+      <c r="J124" t="n">
+        <v>-0.5000000000000004</v>
+      </c>
+      <c r="K124" t="n">
+        <v>25000</v>
+      </c>
+      <c r="L124" t="n">
+        <v>22850</v>
+      </c>
+      <c r="M124" t="n">
+        <v>38753</v>
+      </c>
+      <c r="N124" t="n">
+        <v>23183.33333333333</v>
+      </c>
+      <c r="O124" t="n">
+        <v>29225.66666666667</v>
+      </c>
+      <c r="P124" t="n">
+        <v>159</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>177</v>
+      </c>
+      <c r="R124" t="n">
+        <v>156.6666666666667</v>
+      </c>
+      <c r="S124" t="n">
+        <v>-16</v>
+      </c>
+      <c r="T124" t="n">
+        <v>31</v>
       </c>
     </row>
     <row r="125">
@@ -3560,7 +8206,7 @@
         <v>9</v>
       </c>
       <c r="D125" s="2" t="n">
-        <v>45901</v>
+        <v>45930</v>
       </c>
       <c r="E125" t="n">
         <v>31800</v>
@@ -3569,7 +8215,46 @@
         <v>203</v>
       </c>
       <c r="G125" s="3" t="n">
-        <v>45901</v>
+        <v>45930</v>
+      </c>
+      <c r="H125" t="n">
+        <v>3</v>
+      </c>
+      <c r="I125" t="n">
+        <v>-1</v>
+      </c>
+      <c r="J125" t="n">
+        <v>-1.83697019872103e-16</v>
+      </c>
+      <c r="K125" t="n">
+        <v>22156</v>
+      </c>
+      <c r="L125" t="n">
+        <v>21700</v>
+      </c>
+      <c r="M125" t="n">
+        <v>31455</v>
+      </c>
+      <c r="N125" t="n">
+        <v>22952</v>
+      </c>
+      <c r="O125" t="n">
+        <v>26459.5</v>
+      </c>
+      <c r="P125" t="n">
+        <v>143</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>134</v>
+      </c>
+      <c r="R125" t="n">
+        <v>145.3333333333333</v>
+      </c>
+      <c r="S125" t="n">
+        <v>60</v>
+      </c>
+      <c r="T125" t="n">
+        <v>32</v>
       </c>
     </row>
     <row r="126">
@@ -3585,7 +8270,7 @@
         <v>10</v>
       </c>
       <c r="D126" s="2" t="n">
-        <v>45931</v>
+        <v>45961</v>
       </c>
       <c r="E126" t="n">
         <v>57153</v>
@@ -3594,7 +8279,46 @@
         <v>249</v>
       </c>
       <c r="G126" s="3" t="n">
-        <v>45931</v>
+        <v>45961</v>
+      </c>
+      <c r="H126" t="n">
+        <v>4</v>
+      </c>
+      <c r="I126" t="n">
+        <v>-0.8660254037844386</v>
+      </c>
+      <c r="J126" t="n">
+        <v>0.5000000000000001</v>
+      </c>
+      <c r="K126" t="n">
+        <v>31800</v>
+      </c>
+      <c r="L126" t="n">
+        <v>25000</v>
+      </c>
+      <c r="M126" t="n">
+        <v>35596</v>
+      </c>
+      <c r="N126" t="n">
+        <v>26318.66666666667</v>
+      </c>
+      <c r="O126" t="n">
+        <v>26517</v>
+      </c>
+      <c r="P126" t="n">
+        <v>203</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>159</v>
+      </c>
+      <c r="R126" t="n">
+        <v>168.3333333333333</v>
+      </c>
+      <c r="S126" t="n">
+        <v>46</v>
+      </c>
+      <c r="T126" t="n">
+        <v>33</v>
       </c>
     </row>
     <row r="127">
@@ -3610,7 +8334,7 @@
         <v>11</v>
       </c>
       <c r="D127" s="2" t="n">
-        <v>45962</v>
+        <v>45991</v>
       </c>
       <c r="E127" t="n">
         <v>28900</v>
@@ -3619,7 +8343,46 @@
         <v>185</v>
       </c>
       <c r="G127" s="3" t="n">
-        <v>45962</v>
+        <v>45991</v>
+      </c>
+      <c r="H127" t="n">
+        <v>4</v>
+      </c>
+      <c r="I127" t="n">
+        <v>-0.5000000000000004</v>
+      </c>
+      <c r="J127" t="n">
+        <v>0.8660254037844384</v>
+      </c>
+      <c r="K127" t="n">
+        <v>57153</v>
+      </c>
+      <c r="L127" t="n">
+        <v>22156</v>
+      </c>
+      <c r="M127" t="n">
+        <v>22850</v>
+      </c>
+      <c r="N127" t="n">
+        <v>37036.33333333334</v>
+      </c>
+      <c r="O127" t="n">
+        <v>30109.83333333333</v>
+      </c>
+      <c r="P127" t="n">
+        <v>249</v>
+      </c>
+      <c r="Q127" t="n">
+        <v>143</v>
+      </c>
+      <c r="R127" t="n">
+        <v>198.3333333333333</v>
+      </c>
+      <c r="S127" t="n">
+        <v>-64</v>
+      </c>
+      <c r="T127" t="n">
+        <v>34</v>
       </c>
     </row>
     <row r="128">
@@ -3635,7 +8398,7 @@
         <v>12</v>
       </c>
       <c r="D128" s="2" t="n">
-        <v>45992</v>
+        <v>46022</v>
       </c>
       <c r="E128" t="n">
         <v>27208</v>
@@ -3644,7 +8407,46 @@
         <v>174</v>
       </c>
       <c r="G128" s="3" t="n">
-        <v>45992</v>
+        <v>46022</v>
+      </c>
+      <c r="H128" t="n">
+        <v>4</v>
+      </c>
+      <c r="I128" t="n">
+        <v>-2.449293598294706e-16</v>
+      </c>
+      <c r="J128" t="n">
+        <v>1</v>
+      </c>
+      <c r="K128" t="n">
+        <v>28900</v>
+      </c>
+      <c r="L128" t="n">
+        <v>31800</v>
+      </c>
+      <c r="M128" t="n">
+        <v>21700</v>
+      </c>
+      <c r="N128" t="n">
+        <v>39284.33333333334</v>
+      </c>
+      <c r="O128" t="n">
+        <v>31118.16666666667</v>
+      </c>
+      <c r="P128" t="n">
+        <v>185</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>203</v>
+      </c>
+      <c r="R128" t="n">
+        <v>212.3333333333333</v>
+      </c>
+      <c r="S128" t="n">
+        <v>-11</v>
+      </c>
+      <c r="T128" t="n">
+        <v>35</v>
       </c>
     </row>
   </sheetData>
